--- a/Diabetes.xlsx
+++ b/Diabetes.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A224C340-1B79-4854-A1D3-1BE68386227A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD6328F4-7600-4B2F-A2C1-D437E0B18DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Description" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="92512" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Pregnancies</t>
   </si>
@@ -28,12 +41,6 @@
   </si>
   <si>
     <t>Diabetes</t>
-  </si>
-  <si>
-    <t>Sick</t>
-  </si>
-  <si>
-    <t>Healthy</t>
   </si>
   <si>
     <t>PG_Concentration</t>
@@ -715,22 +722,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>2</v>
@@ -764,8 +771,8 @@
       <c r="H2" s="4">
         <v>50</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>4</v>
+      <c r="I2" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -793,8 +800,8 @@
       <c r="H3" s="4">
         <v>31</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>5</v>
+      <c r="I3" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -822,8 +829,8 @@
       <c r="H4" s="4">
         <v>32</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>4</v>
+      <c r="I4" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -851,8 +858,8 @@
       <c r="H5" s="4">
         <v>21</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>5</v>
+      <c r="I5" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -880,8 +887,8 @@
       <c r="H6" s="4">
         <v>33</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>4</v>
+      <c r="I6" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -909,8 +916,8 @@
       <c r="H7" s="4">
         <v>30</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>5</v>
+      <c r="I7" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -938,8 +945,8 @@
       <c r="H8" s="4">
         <v>26</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>4</v>
+      <c r="I8" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -967,8 +974,8 @@
       <c r="H9" s="4">
         <v>29</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>5</v>
+      <c r="I9" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -996,8 +1003,8 @@
       <c r="H10" s="4">
         <v>53</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>4</v>
+      <c r="I10" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -1025,8 +1032,8 @@
       <c r="H11" s="4">
         <v>54</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>4</v>
+      <c r="I11" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -1054,8 +1061,8 @@
       <c r="H12" s="4">
         <v>30</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>5</v>
+      <c r="I12" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -1083,8 +1090,8 @@
       <c r="H13" s="4">
         <v>34</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>4</v>
+      <c r="I13" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -1112,8 +1119,8 @@
       <c r="H14" s="4">
         <v>57</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>5</v>
+      <c r="I14" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -1141,8 +1148,8 @@
       <c r="H15" s="4">
         <v>59</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>4</v>
+      <c r="I15" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -1170,8 +1177,8 @@
       <c r="H16" s="4">
         <v>51</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>4</v>
+      <c r="I16" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1199,8 +1206,8 @@
       <c r="H17" s="4">
         <v>32</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>4</v>
+      <c r="I17" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1228,8 +1235,8 @@
       <c r="H18" s="4">
         <v>31</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>4</v>
+      <c r="I18" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1257,8 +1264,8 @@
       <c r="H19" s="4">
         <v>31</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>4</v>
+      <c r="I19" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1286,8 +1293,8 @@
       <c r="H20" s="4">
         <v>33</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>5</v>
+      <c r="I20" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -1315,8 +1322,8 @@
       <c r="H21" s="4">
         <v>32</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>4</v>
+      <c r="I21" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
@@ -1344,8 +1351,8 @@
       <c r="H22" s="4">
         <v>27</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>5</v>
+      <c r="I22" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -1373,8 +1380,8 @@
       <c r="H23" s="4">
         <v>50</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>5</v>
+      <c r="I23" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
@@ -1402,8 +1409,8 @@
       <c r="H24" s="4">
         <v>41</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>4</v>
+      <c r="I24" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
@@ -1431,8 +1438,8 @@
       <c r="H25" s="4">
         <v>29</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>4</v>
+      <c r="I25" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -1460,8 +1467,8 @@
       <c r="H26" s="4">
         <v>51</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>4</v>
+      <c r="I26" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
@@ -1489,8 +1496,8 @@
       <c r="H27" s="4">
         <v>41</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>4</v>
+      <c r="I27" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
@@ -1518,8 +1525,8 @@
       <c r="H28" s="4">
         <v>43</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>4</v>
+      <c r="I28" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
@@ -1547,8 +1554,8 @@
       <c r="H29" s="4">
         <v>22</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>5</v>
+      <c r="I29" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
@@ -1576,8 +1583,8 @@
       <c r="H30" s="4">
         <v>57</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>5</v>
+      <c r="I30" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
@@ -1605,8 +1612,8 @@
       <c r="H31" s="4">
         <v>38</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>5</v>
+      <c r="I31" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
@@ -1634,8 +1641,8 @@
       <c r="H32" s="4">
         <v>60</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>5</v>
+      <c r="I32" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -1663,8 +1670,8 @@
       <c r="H33" s="4">
         <v>28</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>4</v>
+      <c r="I33" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
@@ -1692,8 +1699,8 @@
       <c r="H34" s="4">
         <v>22</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>5</v>
+      <c r="I34" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
@@ -1721,8 +1728,8 @@
       <c r="H35" s="4">
         <v>28</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>5</v>
+      <c r="I35" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
@@ -1750,8 +1757,8 @@
       <c r="H36" s="4">
         <v>45</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>5</v>
+      <c r="I36" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
@@ -1779,8 +1786,8 @@
       <c r="H37" s="4">
         <v>33</v>
       </c>
-      <c r="I37" s="4" t="s">
-        <v>5</v>
+      <c r="I37" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
@@ -1808,8 +1815,8 @@
       <c r="H38" s="4">
         <v>35</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>5</v>
+      <c r="I38" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
@@ -1837,8 +1844,8 @@
       <c r="H39" s="4">
         <v>46</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>4</v>
+      <c r="I39" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
@@ -1866,8 +1873,8 @@
       <c r="H40" s="4">
         <v>27</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>4</v>
+      <c r="I40" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
@@ -1895,8 +1902,8 @@
       <c r="H41" s="4">
         <v>56</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>4</v>
+      <c r="I41" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
@@ -1924,8 +1931,8 @@
       <c r="H42" s="4">
         <v>26</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>5</v>
+      <c r="I42" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
@@ -1953,8 +1960,8 @@
       <c r="H43" s="4">
         <v>37</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>5</v>
+      <c r="I43" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
@@ -1982,8 +1989,8 @@
       <c r="H44" s="4">
         <v>48</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>5</v>
+      <c r="I44" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
@@ -2011,8 +2018,8 @@
       <c r="H45" s="4">
         <v>54</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>4</v>
+      <c r="I45" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
@@ -2040,8 +2047,8 @@
       <c r="H46" s="4">
         <v>40</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>5</v>
+      <c r="I46" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
@@ -2069,8 +2076,8 @@
       <c r="H47" s="4">
         <v>25</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>4</v>
+      <c r="I47" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
@@ -2098,8 +2105,8 @@
       <c r="H48" s="4">
         <v>29</v>
       </c>
-      <c r="I48" s="4" t="s">
-        <v>5</v>
+      <c r="I48" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
@@ -2127,8 +2134,8 @@
       <c r="H49" s="4">
         <v>22</v>
       </c>
-      <c r="I49" s="4" t="s">
-        <v>5</v>
+      <c r="I49" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
@@ -2156,8 +2163,8 @@
       <c r="H50" s="4">
         <v>31</v>
       </c>
-      <c r="I50" s="4" t="s">
-        <v>4</v>
+      <c r="I50" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
@@ -2185,8 +2192,8 @@
       <c r="H51" s="4">
         <v>24</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>5</v>
+      <c r="I51" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
@@ -2214,8 +2221,8 @@
       <c r="H52" s="4">
         <v>22</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>5</v>
+      <c r="I52" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
@@ -2243,8 +2250,8 @@
       <c r="H53" s="4">
         <v>26</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>5</v>
+      <c r="I53" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
@@ -2272,8 +2279,8 @@
       <c r="H54" s="4">
         <v>30</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>5</v>
+      <c r="I54" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
@@ -2301,8 +2308,8 @@
       <c r="H55" s="4">
         <v>58</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>4</v>
+      <c r="I55" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
@@ -2330,8 +2337,8 @@
       <c r="H56" s="4">
         <v>42</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>5</v>
+      <c r="I56" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
@@ -2359,8 +2366,8 @@
       <c r="H57" s="4">
         <v>21</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>5</v>
+      <c r="I57" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
@@ -2388,8 +2395,8 @@
       <c r="H58" s="4">
         <v>41</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>4</v>
+      <c r="I58" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
@@ -2417,8 +2424,8 @@
       <c r="H59" s="4">
         <v>31</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>5</v>
+      <c r="I59" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
@@ -2446,8 +2453,8 @@
       <c r="H60" s="4">
         <v>44</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>5</v>
+      <c r="I60" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
@@ -2475,8 +2482,8 @@
       <c r="H61" s="4">
         <v>22</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>5</v>
+      <c r="I61" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
@@ -2504,8 +2511,8 @@
       <c r="H62" s="4">
         <v>21</v>
       </c>
-      <c r="I62" s="4" t="s">
-        <v>5</v>
+      <c r="I62" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
@@ -2533,8 +2540,8 @@
       <c r="H63" s="4">
         <v>39</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>4</v>
+      <c r="I63" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
@@ -2562,8 +2569,8 @@
       <c r="H64" s="4">
         <v>36</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>5</v>
+      <c r="I64" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
@@ -2591,8 +2598,8 @@
       <c r="H65" s="4">
         <v>24</v>
       </c>
-      <c r="I65" s="4" t="s">
-        <v>5</v>
+      <c r="I65" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
@@ -2620,8 +2627,8 @@
       <c r="H66" s="4">
         <v>42</v>
       </c>
-      <c r="I66" s="4" t="s">
-        <v>4</v>
+      <c r="I66" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
@@ -2649,8 +2656,8 @@
       <c r="H67" s="4">
         <v>32</v>
       </c>
-      <c r="I67" s="4" t="s">
-        <v>5</v>
+      <c r="I67" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
@@ -2678,8 +2685,8 @@
       <c r="H68" s="4">
         <v>38</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>4</v>
+      <c r="I68" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
@@ -2707,8 +2714,8 @@
       <c r="H69" s="4">
         <v>54</v>
       </c>
-      <c r="I69" s="4" t="s">
-        <v>5</v>
+      <c r="I69" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
@@ -2736,8 +2743,8 @@
       <c r="H70" s="4">
         <v>25</v>
       </c>
-      <c r="I70" s="4" t="s">
-        <v>5</v>
+      <c r="I70" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
@@ -2765,8 +2772,8 @@
       <c r="H71" s="4">
         <v>27</v>
       </c>
-      <c r="I71" s="4" t="s">
-        <v>5</v>
+      <c r="I71" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
@@ -2794,8 +2801,8 @@
       <c r="H72" s="4">
         <v>28</v>
       </c>
-      <c r="I72" s="4" t="s">
-        <v>4</v>
+      <c r="I72" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
@@ -2823,8 +2830,8 @@
       <c r="H73" s="4">
         <v>26</v>
       </c>
-      <c r="I73" s="4" t="s">
-        <v>5</v>
+      <c r="I73" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
@@ -2852,8 +2859,8 @@
       <c r="H74" s="4">
         <v>42</v>
       </c>
-      <c r="I74" s="4" t="s">
-        <v>4</v>
+      <c r="I74" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -2881,8 +2888,8 @@
       <c r="H75" s="4">
         <v>23</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>5</v>
+      <c r="I75" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -2910,8 +2917,8 @@
       <c r="H76" s="4">
         <v>22</v>
       </c>
-      <c r="I76" s="4" t="s">
-        <v>5</v>
+      <c r="I76" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -2939,8 +2946,8 @@
       <c r="H77" s="4">
         <v>22</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>5</v>
+      <c r="I77" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -2968,8 +2975,8 @@
       <c r="H78" s="4">
         <v>41</v>
       </c>
-      <c r="I78" s="4" t="s">
-        <v>5</v>
+      <c r="I78" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -2997,8 +3004,8 @@
       <c r="H79" s="4">
         <v>27</v>
       </c>
-      <c r="I79" s="4" t="s">
-        <v>5</v>
+      <c r="I79" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -3026,8 +3033,8 @@
       <c r="H80" s="4">
         <v>26</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>4</v>
+      <c r="I80" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
@@ -3055,8 +3062,8 @@
       <c r="H81" s="4">
         <v>24</v>
       </c>
-      <c r="I81" s="4" t="s">
-        <v>5</v>
+      <c r="I81" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
@@ -3084,8 +3091,8 @@
       <c r="H82" s="4">
         <v>22</v>
       </c>
-      <c r="I82" s="4" t="s">
-        <v>5</v>
+      <c r="I82" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
@@ -3113,8 +3120,8 @@
       <c r="H83" s="4">
         <v>22</v>
       </c>
-      <c r="I83" s="4" t="s">
-        <v>5</v>
+      <c r="I83" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
@@ -3142,8 +3149,8 @@
       <c r="H84" s="4">
         <v>36</v>
       </c>
-      <c r="I84" s="4" t="s">
-        <v>5</v>
+      <c r="I84" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
@@ -3171,8 +3178,8 @@
       <c r="H85" s="4">
         <v>22</v>
       </c>
-      <c r="I85" s="4" t="s">
-        <v>5</v>
+      <c r="I85" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
@@ -3200,8 +3207,8 @@
       <c r="H86" s="4">
         <v>37</v>
       </c>
-      <c r="I86" s="4" t="s">
-        <v>4</v>
+      <c r="I86" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
@@ -3229,8 +3236,8 @@
       <c r="H87" s="4">
         <v>27</v>
       </c>
-      <c r="I87" s="4" t="s">
-        <v>5</v>
+      <c r="I87" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
@@ -3258,8 +3265,8 @@
       <c r="H88" s="4">
         <v>45</v>
       </c>
-      <c r="I88" s="4" t="s">
-        <v>5</v>
+      <c r="I88" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
@@ -3287,8 +3294,8 @@
       <c r="H89" s="4">
         <v>26</v>
       </c>
-      <c r="I89" s="4" t="s">
-        <v>5</v>
+      <c r="I89" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
@@ -3316,8 +3323,8 @@
       <c r="H90" s="4">
         <v>43</v>
       </c>
-      <c r="I90" s="4" t="s">
-        <v>4</v>
+      <c r="I90" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
@@ -3345,8 +3352,8 @@
       <c r="H91" s="4">
         <v>24</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>5</v>
+      <c r="I91" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
@@ -3374,8 +3381,8 @@
       <c r="H92" s="4">
         <v>21</v>
       </c>
-      <c r="I92" s="4" t="s">
-        <v>5</v>
+      <c r="I92" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
@@ -3403,8 +3410,8 @@
       <c r="H93" s="4">
         <v>34</v>
       </c>
-      <c r="I93" s="4" t="s">
-        <v>5</v>
+      <c r="I93" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
@@ -3432,8 +3439,8 @@
       <c r="H94" s="4">
         <v>42</v>
       </c>
-      <c r="I94" s="4" t="s">
-        <v>5</v>
+      <c r="I94" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
@@ -3461,8 +3468,8 @@
       <c r="H95" s="4">
         <v>60</v>
       </c>
-      <c r="I95" s="4" t="s">
-        <v>4</v>
+      <c r="I95" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
@@ -3490,8 +3497,8 @@
       <c r="H96" s="4">
         <v>21</v>
       </c>
-      <c r="I96" s="4" t="s">
-        <v>5</v>
+      <c r="I96" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
@@ -3519,8 +3526,8 @@
       <c r="H97" s="4">
         <v>40</v>
       </c>
-      <c r="I97" s="4" t="s">
-        <v>5</v>
+      <c r="I97" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
@@ -3548,8 +3555,8 @@
       <c r="H98" s="4">
         <v>24</v>
       </c>
-      <c r="I98" s="4" t="s">
-        <v>5</v>
+      <c r="I98" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
@@ -3577,8 +3584,8 @@
       <c r="H99" s="4">
         <v>22</v>
       </c>
-      <c r="I99" s="4" t="s">
-        <v>5</v>
+      <c r="I99" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
@@ -3606,8 +3613,8 @@
       <c r="H100" s="4">
         <v>23</v>
       </c>
-      <c r="I100" s="4" t="s">
-        <v>5</v>
+      <c r="I100" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
@@ -3635,8 +3642,8 @@
       <c r="H101" s="4">
         <v>31</v>
       </c>
-      <c r="I101" s="4" t="s">
-        <v>4</v>
+      <c r="I101" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
@@ -3664,8 +3671,8 @@
       <c r="H102" s="4">
         <v>33</v>
       </c>
-      <c r="I102" s="4" t="s">
-        <v>4</v>
+      <c r="I102" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
@@ -3693,8 +3700,8 @@
       <c r="H103" s="4">
         <v>22</v>
       </c>
-      <c r="I103" s="4" t="s">
-        <v>5</v>
+      <c r="I103" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
@@ -3722,8 +3729,8 @@
       <c r="H104" s="4">
         <v>21</v>
       </c>
-      <c r="I104" s="4" t="s">
-        <v>5</v>
+      <c r="I104" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
@@ -3751,8 +3758,8 @@
       <c r="H105" s="4">
         <v>24</v>
       </c>
-      <c r="I105" s="4" t="s">
-        <v>5</v>
+      <c r="I105" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
@@ -3780,8 +3787,8 @@
       <c r="H106" s="4">
         <v>27</v>
       </c>
-      <c r="I106" s="4" t="s">
-        <v>5</v>
+      <c r="I106" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
@@ -3809,8 +3816,8 @@
       <c r="H107" s="4">
         <v>21</v>
       </c>
-      <c r="I107" s="4" t="s">
-        <v>5</v>
+      <c r="I107" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
@@ -3838,8 +3845,8 @@
       <c r="H108" s="4">
         <v>27</v>
       </c>
-      <c r="I108" s="4" t="s">
-        <v>5</v>
+      <c r="I108" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
@@ -3867,8 +3874,8 @@
       <c r="H109" s="4">
         <v>37</v>
       </c>
-      <c r="I109" s="4" t="s">
-        <v>5</v>
+      <c r="I109" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
@@ -3896,8 +3903,8 @@
       <c r="H110" s="4">
         <v>25</v>
       </c>
-      <c r="I110" s="4" t="s">
-        <v>5</v>
+      <c r="I110" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
@@ -3925,8 +3932,8 @@
       <c r="H111" s="4">
         <v>24</v>
       </c>
-      <c r="I111" s="4" t="s">
-        <v>4</v>
+      <c r="I111" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
@@ -3954,8 +3961,8 @@
       <c r="H112" s="4">
         <v>24</v>
       </c>
-      <c r="I112" s="4" t="s">
-        <v>4</v>
+      <c r="I112" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
@@ -3983,8 +3990,8 @@
       <c r="H113" s="4">
         <v>46</v>
       </c>
-      <c r="I113" s="4" t="s">
-        <v>4</v>
+      <c r="I113" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
@@ -4012,8 +4019,8 @@
       <c r="H114" s="4">
         <v>23</v>
       </c>
-      <c r="I114" s="4" t="s">
-        <v>5</v>
+      <c r="I114" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
@@ -4041,8 +4048,8 @@
       <c r="H115" s="4">
         <v>25</v>
       </c>
-      <c r="I115" s="4" t="s">
-        <v>5</v>
+      <c r="I115" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
@@ -4070,8 +4077,8 @@
       <c r="H116" s="4">
         <v>39</v>
       </c>
-      <c r="I116" s="4" t="s">
-        <v>4</v>
+      <c r="I116" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
@@ -4099,8 +4106,8 @@
       <c r="H117" s="4">
         <v>61</v>
       </c>
-      <c r="I117" s="4" t="s">
-        <v>4</v>
+      <c r="I117" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
@@ -4128,8 +4135,8 @@
       <c r="H118" s="4">
         <v>38</v>
       </c>
-      <c r="I118" s="4" t="s">
-        <v>4</v>
+      <c r="I118" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
@@ -4157,8 +4164,8 @@
       <c r="H119" s="4">
         <v>25</v>
       </c>
-      <c r="I119" s="4" t="s">
-        <v>5</v>
+      <c r="I119" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
@@ -4186,8 +4193,8 @@
       <c r="H120" s="4">
         <v>22</v>
       </c>
-      <c r="I120" s="4" t="s">
-        <v>5</v>
+      <c r="I120" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
@@ -4215,8 +4222,8 @@
       <c r="H121" s="4">
         <v>21</v>
       </c>
-      <c r="I121" s="4" t="s">
-        <v>5</v>
+      <c r="I121" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
@@ -4244,8 +4251,8 @@
       <c r="H122" s="4">
         <v>25</v>
       </c>
-      <c r="I122" s="4" t="s">
-        <v>4</v>
+      <c r="I122" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
@@ -4273,8 +4280,8 @@
       <c r="H123" s="4">
         <v>24</v>
       </c>
-      <c r="I123" s="4" t="s">
-        <v>5</v>
+      <c r="I123" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
@@ -4302,8 +4309,8 @@
       <c r="H124" s="4">
         <v>23</v>
       </c>
-      <c r="I124" s="4" t="s">
-        <v>5</v>
+      <c r="I124" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
@@ -4331,8 +4338,8 @@
       <c r="H125" s="4">
         <v>69</v>
       </c>
-      <c r="I125" s="4" t="s">
-        <v>5</v>
+      <c r="I125" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
@@ -4360,8 +4367,8 @@
       <c r="H126" s="4">
         <v>23</v>
       </c>
-      <c r="I126" s="4" t="s">
-        <v>4</v>
+      <c r="I126" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
@@ -4389,8 +4396,8 @@
       <c r="H127" s="4">
         <v>26</v>
       </c>
-      <c r="I127" s="4" t="s">
-        <v>4</v>
+      <c r="I127" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
@@ -4418,8 +4425,8 @@
       <c r="H128" s="4">
         <v>30</v>
       </c>
-      <c r="I128" s="4" t="s">
-        <v>5</v>
+      <c r="I128" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
@@ -4447,8 +4454,8 @@
       <c r="H129" s="4">
         <v>23</v>
       </c>
-      <c r="I129" s="4" t="s">
-        <v>5</v>
+      <c r="I129" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
@@ -4476,8 +4483,8 @@
       <c r="H130" s="4">
         <v>40</v>
       </c>
-      <c r="I130" s="4" t="s">
-        <v>4</v>
+      <c r="I130" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
@@ -4505,8 +4512,8 @@
       <c r="H131" s="4">
         <v>62</v>
       </c>
-      <c r="I131" s="4" t="s">
-        <v>4</v>
+      <c r="I131" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
@@ -4534,8 +4541,8 @@
       <c r="H132" s="4">
         <v>33</v>
       </c>
-      <c r="I132" s="4" t="s">
-        <v>4</v>
+      <c r="I132" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
@@ -4563,8 +4570,8 @@
       <c r="H133" s="4">
         <v>33</v>
       </c>
-      <c r="I133" s="4" t="s">
-        <v>4</v>
+      <c r="I133" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
@@ -4592,8 +4599,8 @@
       <c r="H134" s="4">
         <v>30</v>
       </c>
-      <c r="I134" s="4" t="s">
-        <v>4</v>
+      <c r="I134" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
@@ -4621,8 +4628,8 @@
       <c r="H135" s="4">
         <v>39</v>
       </c>
-      <c r="I135" s="4" t="s">
-        <v>5</v>
+      <c r="I135" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
@@ -4650,8 +4657,8 @@
       <c r="H136" s="4">
         <v>26</v>
       </c>
-      <c r="I136" s="4" t="s">
-        <v>5</v>
+      <c r="I136" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
@@ -4679,8 +4686,8 @@
       <c r="H137" s="4">
         <v>31</v>
       </c>
-      <c r="I137" s="4" t="s">
-        <v>5</v>
+      <c r="I137" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
@@ -4708,8 +4715,8 @@
       <c r="H138" s="4">
         <v>21</v>
       </c>
-      <c r="I138" s="4" t="s">
-        <v>5</v>
+      <c r="I138" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
@@ -4737,8 +4744,8 @@
       <c r="H139" s="4">
         <v>22</v>
       </c>
-      <c r="I139" s="4" t="s">
-        <v>5</v>
+      <c r="I139" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
@@ -4766,8 +4773,8 @@
       <c r="H140" s="4">
         <v>29</v>
       </c>
-      <c r="I140" s="4" t="s">
-        <v>5</v>
+      <c r="I140" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
@@ -4795,8 +4802,8 @@
       <c r="H141" s="4">
         <v>28</v>
       </c>
-      <c r="I141" s="4" t="s">
-        <v>5</v>
+      <c r="I141" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
@@ -4824,8 +4831,8 @@
       <c r="H142" s="4">
         <v>55</v>
       </c>
-      <c r="I142" s="4" t="s">
-        <v>5</v>
+      <c r="I142" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
@@ -4853,8 +4860,8 @@
       <c r="H143" s="4">
         <v>38</v>
       </c>
-      <c r="I143" s="4" t="s">
-        <v>5</v>
+      <c r="I143" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
@@ -4882,8 +4889,8 @@
       <c r="H144" s="4">
         <v>22</v>
       </c>
-      <c r="I144" s="4" t="s">
-        <v>5</v>
+      <c r="I144" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
@@ -4911,8 +4918,8 @@
       <c r="H145" s="4">
         <v>42</v>
       </c>
-      <c r="I145" s="4" t="s">
-        <v>4</v>
+      <c r="I145" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
@@ -4940,8 +4947,8 @@
       <c r="H146" s="4">
         <v>23</v>
       </c>
-      <c r="I146" s="4" t="s">
-        <v>5</v>
+      <c r="I146" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
@@ -4969,8 +4976,8 @@
       <c r="H147" s="4">
         <v>21</v>
       </c>
-      <c r="I147" s="4" t="s">
-        <v>5</v>
+      <c r="I147" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
@@ -4998,8 +5005,8 @@
       <c r="H148" s="4">
         <v>41</v>
       </c>
-      <c r="I148" s="4" t="s">
-        <v>5</v>
+      <c r="I148" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
@@ -5027,8 +5034,8 @@
       <c r="H149" s="4">
         <v>34</v>
       </c>
-      <c r="I149" s="4" t="s">
-        <v>5</v>
+      <c r="I149" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
@@ -5056,8 +5063,8 @@
       <c r="H150" s="4">
         <v>65</v>
       </c>
-      <c r="I150" s="4" t="s">
-        <v>5</v>
+      <c r="I150" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
@@ -5085,8 +5092,8 @@
       <c r="H151" s="4">
         <v>22</v>
       </c>
-      <c r="I151" s="4" t="s">
-        <v>5</v>
+      <c r="I151" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
@@ -5114,8 +5121,8 @@
       <c r="H152" s="4">
         <v>24</v>
       </c>
-      <c r="I152" s="4" t="s">
-        <v>5</v>
+      <c r="I152" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
@@ -5143,8 +5150,8 @@
       <c r="H153" s="4">
         <v>37</v>
       </c>
-      <c r="I153" s="4" t="s">
-        <v>5</v>
+      <c r="I153" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
@@ -5172,8 +5179,8 @@
       <c r="H154" s="4">
         <v>42</v>
       </c>
-      <c r="I154" s="4" t="s">
-        <v>4</v>
+      <c r="I154" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
@@ -5201,8 +5208,8 @@
       <c r="H155" s="4">
         <v>23</v>
       </c>
-      <c r="I155" s="4" t="s">
-        <v>5</v>
+      <c r="I155" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
@@ -5230,8 +5237,8 @@
       <c r="H156" s="4">
         <v>43</v>
       </c>
-      <c r="I156" s="4" t="s">
-        <v>4</v>
+      <c r="I156" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
@@ -5259,8 +5266,8 @@
       <c r="H157" s="4">
         <v>36</v>
       </c>
-      <c r="I157" s="4" t="s">
-        <v>4</v>
+      <c r="I157" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
@@ -5288,8 +5295,8 @@
       <c r="H158" s="4">
         <v>21</v>
       </c>
-      <c r="I158" s="4" t="s">
-        <v>5</v>
+      <c r="I158" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
@@ -5317,8 +5324,8 @@
       <c r="H159" s="4">
         <v>23</v>
       </c>
-      <c r="I159" s="4" t="s">
-        <v>5</v>
+      <c r="I159" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
@@ -5346,8 +5353,8 @@
       <c r="H160" s="4">
         <v>22</v>
       </c>
-      <c r="I160" s="4" t="s">
-        <v>5</v>
+      <c r="I160" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
@@ -5375,8 +5382,8 @@
       <c r="H161" s="4">
         <v>47</v>
       </c>
-      <c r="I161" s="4" t="s">
-        <v>4</v>
+      <c r="I161" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
@@ -5404,8 +5411,8 @@
       <c r="H162" s="4">
         <v>36</v>
       </c>
-      <c r="I162" s="4" t="s">
-        <v>5</v>
+      <c r="I162" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
@@ -5433,8 +5440,8 @@
       <c r="H163" s="4">
         <v>45</v>
       </c>
-      <c r="I163" s="4" t="s">
-        <v>5</v>
+      <c r="I163" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
@@ -5462,8 +5469,8 @@
       <c r="H164" s="4">
         <v>27</v>
       </c>
-      <c r="I164" s="4" t="s">
-        <v>5</v>
+      <c r="I164" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
@@ -5491,8 +5498,8 @@
       <c r="H165" s="4">
         <v>21</v>
       </c>
-      <c r="I165" s="4" t="s">
-        <v>5</v>
+      <c r="I165" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
@@ -5520,8 +5527,8 @@
       <c r="H166" s="4">
         <v>32</v>
       </c>
-      <c r="I166" s="4" t="s">
-        <v>4</v>
+      <c r="I166" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
@@ -5549,8 +5556,8 @@
       <c r="H167" s="4">
         <v>41</v>
       </c>
-      <c r="I167" s="4" t="s">
-        <v>4</v>
+      <c r="I167" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
@@ -5578,8 +5585,8 @@
       <c r="H168" s="4">
         <v>22</v>
       </c>
-      <c r="I168" s="4" t="s">
-        <v>5</v>
+      <c r="I168" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
@@ -5607,8 +5614,8 @@
       <c r="H169" s="4">
         <v>34</v>
       </c>
-      <c r="I169" s="4" t="s">
-        <v>5</v>
+      <c r="I169" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
@@ -5636,8 +5643,8 @@
       <c r="H170" s="4">
         <v>29</v>
       </c>
-      <c r="I170" s="4" t="s">
-        <v>5</v>
+      <c r="I170" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
@@ -5665,8 +5672,8 @@
       <c r="H171" s="4">
         <v>29</v>
       </c>
-      <c r="I171" s="4" t="s">
-        <v>5</v>
+      <c r="I171" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
@@ -5694,8 +5701,8 @@
       <c r="H172" s="4">
         <v>36</v>
       </c>
-      <c r="I172" s="4" t="s">
-        <v>4</v>
+      <c r="I172" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
@@ -5723,8 +5730,8 @@
       <c r="H173" s="4">
         <v>29</v>
       </c>
-      <c r="I173" s="4" t="s">
-        <v>4</v>
+      <c r="I173" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
@@ -5752,8 +5759,8 @@
       <c r="H174" s="4">
         <v>25</v>
       </c>
-      <c r="I174" s="4" t="s">
-        <v>5</v>
+      <c r="I174" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
@@ -5781,8 +5788,8 @@
       <c r="H175" s="4">
         <v>23</v>
       </c>
-      <c r="I175" s="4" t="s">
-        <v>5</v>
+      <c r="I175" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
@@ -5810,8 +5817,8 @@
       <c r="H176" s="4">
         <v>33</v>
       </c>
-      <c r="I176" s="4" t="s">
-        <v>5</v>
+      <c r="I176" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
@@ -5839,8 +5846,8 @@
       <c r="H177" s="4">
         <v>36</v>
       </c>
-      <c r="I177" s="4" t="s">
-        <v>4</v>
+      <c r="I177" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
@@ -5868,8 +5875,8 @@
       <c r="H178" s="4">
         <v>42</v>
       </c>
-      <c r="I178" s="4" t="s">
-        <v>5</v>
+      <c r="I178" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
@@ -5897,8 +5904,8 @@
       <c r="H179" s="4">
         <v>26</v>
       </c>
-      <c r="I179" s="4" t="s">
-        <v>4</v>
+      <c r="I179" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
@@ -5926,8 +5933,8 @@
       <c r="H180" s="4">
         <v>47</v>
       </c>
-      <c r="I180" s="4" t="s">
-        <v>5</v>
+      <c r="I180" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
@@ -5955,8 +5962,8 @@
       <c r="H181" s="4">
         <v>37</v>
       </c>
-      <c r="I181" s="4" t="s">
-        <v>4</v>
+      <c r="I181" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
@@ -5984,8 +5991,8 @@
       <c r="H182" s="4">
         <v>32</v>
       </c>
-      <c r="I182" s="4" t="s">
-        <v>5</v>
+      <c r="I182" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
@@ -6013,8 +6020,8 @@
       <c r="H183" s="4">
         <v>23</v>
       </c>
-      <c r="I183" s="4" t="s">
-        <v>5</v>
+      <c r="I183" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
@@ -6042,8 +6049,8 @@
       <c r="H184" s="4">
         <v>21</v>
       </c>
-      <c r="I184" s="4" t="s">
-        <v>5</v>
+      <c r="I184" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
@@ -6071,8 +6078,8 @@
       <c r="H185" s="4">
         <v>27</v>
       </c>
-      <c r="I185" s="4" t="s">
-        <v>5</v>
+      <c r="I185" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
@@ -6100,8 +6107,8 @@
       <c r="H186" s="4">
         <v>40</v>
       </c>
-      <c r="I186" s="4" t="s">
-        <v>5</v>
+      <c r="I186" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
@@ -6129,8 +6136,8 @@
       <c r="H187" s="4">
         <v>41</v>
       </c>
-      <c r="I187" s="4" t="s">
-        <v>4</v>
+      <c r="I187" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
@@ -6158,8 +6165,8 @@
       <c r="H188" s="4">
         <v>60</v>
       </c>
-      <c r="I188" s="4" t="s">
-        <v>4</v>
+      <c r="I188" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
@@ -6187,8 +6194,8 @@
       <c r="H189" s="4">
         <v>33</v>
       </c>
-      <c r="I189" s="4" t="s">
-        <v>4</v>
+      <c r="I189" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
@@ -6216,8 +6223,8 @@
       <c r="H190" s="4">
         <v>31</v>
       </c>
-      <c r="I190" s="4" t="s">
-        <v>4</v>
+      <c r="I190" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
@@ -6245,8 +6252,8 @@
       <c r="H191" s="4">
         <v>25</v>
       </c>
-      <c r="I191" s="4" t="s">
-        <v>4</v>
+      <c r="I191" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
@@ -6274,8 +6281,8 @@
       <c r="H192" s="4">
         <v>21</v>
       </c>
-      <c r="I192" s="4" t="s">
-        <v>5</v>
+      <c r="I192" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
@@ -6303,8 +6310,8 @@
       <c r="H193" s="4">
         <v>40</v>
       </c>
-      <c r="I193" s="4" t="s">
-        <v>5</v>
+      <c r="I193" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
@@ -6332,8 +6339,8 @@
       <c r="H194" s="4">
         <v>36</v>
       </c>
-      <c r="I194" s="4" t="s">
-        <v>4</v>
+      <c r="I194" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
@@ -6361,8 +6368,8 @@
       <c r="H195" s="4">
         <v>40</v>
       </c>
-      <c r="I195" s="4" t="s">
-        <v>4</v>
+      <c r="I195" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
@@ -6390,8 +6397,8 @@
       <c r="H196" s="4">
         <v>42</v>
       </c>
-      <c r="I196" s="4" t="s">
-        <v>5</v>
+      <c r="I196" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
@@ -6419,8 +6426,8 @@
       <c r="H197" s="4">
         <v>29</v>
       </c>
-      <c r="I197" s="4" t="s">
-        <v>4</v>
+      <c r="I197" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
@@ -6448,8 +6455,8 @@
       <c r="H198" s="4">
         <v>21</v>
       </c>
-      <c r="I198" s="4" t="s">
-        <v>5</v>
+      <c r="I198" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
@@ -6477,8 +6484,8 @@
       <c r="H199" s="4">
         <v>23</v>
       </c>
-      <c r="I199" s="4" t="s">
-        <v>4</v>
+      <c r="I199" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
@@ -6506,8 +6513,8 @@
       <c r="H200" s="4">
         <v>26</v>
       </c>
-      <c r="I200" s="4" t="s">
-        <v>4</v>
+      <c r="I200" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
@@ -6535,8 +6542,8 @@
       <c r="H201" s="4">
         <v>29</v>
       </c>
-      <c r="I201" s="4" t="s">
-        <v>4</v>
+      <c r="I201" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
@@ -6564,8 +6571,8 @@
       <c r="H202" s="4">
         <v>21</v>
       </c>
-      <c r="I202" s="4" t="s">
-        <v>5</v>
+      <c r="I202" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
@@ -6593,8 +6600,8 @@
       <c r="H203" s="4">
         <v>28</v>
       </c>
-      <c r="I203" s="4" t="s">
-        <v>5</v>
+      <c r="I203" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
@@ -6622,8 +6629,8 @@
       <c r="H204" s="4">
         <v>32</v>
       </c>
-      <c r="I204" s="4" t="s">
-        <v>5</v>
+      <c r="I204" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
@@ -6651,8 +6658,8 @@
       <c r="H205" s="4">
         <v>27</v>
       </c>
-      <c r="I205" s="4" t="s">
-        <v>5</v>
+      <c r="I205" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
@@ -6680,8 +6687,8 @@
       <c r="H206" s="4">
         <v>55</v>
       </c>
-      <c r="I206" s="4" t="s">
-        <v>5</v>
+      <c r="I206" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
@@ -6709,8 +6716,8 @@
       <c r="H207" s="4">
         <v>27</v>
       </c>
-      <c r="I207" s="4" t="s">
-        <v>5</v>
+      <c r="I207" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
@@ -6738,8 +6745,8 @@
       <c r="H208" s="4">
         <v>57</v>
       </c>
-      <c r="I208" s="4" t="s">
-        <v>4</v>
+      <c r="I208" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
@@ -6767,8 +6774,8 @@
       <c r="H209" s="4">
         <v>52</v>
       </c>
-      <c r="I209" s="4" t="s">
-        <v>4</v>
+      <c r="I209" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
@@ -6796,8 +6803,8 @@
       <c r="H210" s="4">
         <v>21</v>
       </c>
-      <c r="I210" s="4" t="s">
-        <v>5</v>
+      <c r="I210" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
@@ -6825,8 +6832,8 @@
       <c r="H211" s="4">
         <v>41</v>
       </c>
-      <c r="I211" s="4" t="s">
-        <v>4</v>
+      <c r="I211" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
@@ -6854,8 +6861,8 @@
       <c r="H212" s="4">
         <v>25</v>
       </c>
-      <c r="I212" s="4" t="s">
-        <v>5</v>
+      <c r="I212" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
@@ -6883,8 +6890,8 @@
       <c r="H213" s="4">
         <v>24</v>
       </c>
-      <c r="I213" s="4" t="s">
-        <v>5</v>
+      <c r="I213" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
@@ -6912,8 +6919,8 @@
       <c r="H214" s="4">
         <v>60</v>
       </c>
-      <c r="I214" s="4" t="s">
-        <v>5</v>
+      <c r="I214" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
@@ -6941,8 +6948,8 @@
       <c r="H215" s="4">
         <v>24</v>
       </c>
-      <c r="I215" s="4" t="s">
-        <v>4</v>
+      <c r="I215" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
@@ -6970,8 +6977,8 @@
       <c r="H216" s="4">
         <v>36</v>
       </c>
-      <c r="I216" s="4" t="s">
-        <v>4</v>
+      <c r="I216" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
@@ -6999,8 +7006,8 @@
       <c r="H217" s="4">
         <v>38</v>
       </c>
-      <c r="I217" s="4" t="s">
-        <v>4</v>
+      <c r="I217" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
@@ -7028,8 +7035,8 @@
       <c r="H218" s="4">
         <v>25</v>
       </c>
-      <c r="I218" s="4" t="s">
-        <v>4</v>
+      <c r="I218" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
@@ -7057,8 +7064,8 @@
       <c r="H219" s="4">
         <v>32</v>
       </c>
-      <c r="I219" s="4" t="s">
-        <v>5</v>
+      <c r="I219" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
@@ -7086,8 +7093,8 @@
       <c r="H220" s="4">
         <v>32</v>
       </c>
-      <c r="I220" s="4" t="s">
-        <v>4</v>
+      <c r="I220" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
@@ -7115,8 +7122,8 @@
       <c r="H221" s="4">
         <v>41</v>
       </c>
-      <c r="I221" s="4" t="s">
-        <v>4</v>
+      <c r="I221" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
@@ -7144,8 +7151,8 @@
       <c r="H222" s="4">
         <v>21</v>
       </c>
-      <c r="I222" s="4" t="s">
-        <v>4</v>
+      <c r="I222" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
@@ -7173,8 +7180,8 @@
       <c r="H223" s="4">
         <v>66</v>
       </c>
-      <c r="I223" s="4" t="s">
-        <v>4</v>
+      <c r="I223" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
@@ -7202,8 +7209,8 @@
       <c r="H224" s="4">
         <v>37</v>
       </c>
-      <c r="I224" s="4" t="s">
-        <v>5</v>
+      <c r="I224" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
@@ -7231,8 +7238,8 @@
       <c r="H225" s="4">
         <v>61</v>
       </c>
-      <c r="I225" s="4" t="s">
-        <v>5</v>
+      <c r="I225" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
@@ -7260,8 +7267,8 @@
       <c r="H226" s="4">
         <v>26</v>
       </c>
-      <c r="I226" s="4" t="s">
-        <v>5</v>
+      <c r="I226" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
@@ -7289,8 +7296,8 @@
       <c r="H227" s="4">
         <v>22</v>
       </c>
-      <c r="I227" s="4" t="s">
-        <v>5</v>
+      <c r="I227" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
@@ -7318,8 +7325,8 @@
       <c r="H228" s="4">
         <v>26</v>
       </c>
-      <c r="I228" s="4" t="s">
-        <v>5</v>
+      <c r="I228" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
@@ -7347,8 +7354,8 @@
       <c r="H229" s="4">
         <v>24</v>
       </c>
-      <c r="I229" s="4" t="s">
-        <v>4</v>
+      <c r="I229" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
@@ -7376,8 +7383,8 @@
       <c r="H230" s="4">
         <v>31</v>
       </c>
-      <c r="I230" s="4" t="s">
-        <v>5</v>
+      <c r="I230" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
@@ -7405,8 +7412,8 @@
       <c r="H231" s="4">
         <v>24</v>
       </c>
-      <c r="I231" s="4" t="s">
-        <v>5</v>
+      <c r="I231" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
@@ -7434,8 +7441,8 @@
       <c r="H232" s="4">
         <v>22</v>
       </c>
-      <c r="I232" s="4" t="s">
-        <v>4</v>
+      <c r="I232" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
@@ -7463,8 +7470,8 @@
       <c r="H233" s="4">
         <v>46</v>
       </c>
-      <c r="I233" s="4" t="s">
-        <v>4</v>
+      <c r="I233" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
@@ -7492,8 +7499,8 @@
       <c r="H234" s="4">
         <v>22</v>
       </c>
-      <c r="I234" s="4" t="s">
-        <v>5</v>
+      <c r="I234" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
@@ -7521,8 +7528,8 @@
       <c r="H235" s="4">
         <v>29</v>
       </c>
-      <c r="I235" s="4" t="s">
-        <v>5</v>
+      <c r="I235" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
@@ -7550,8 +7557,8 @@
       <c r="H236" s="4">
         <v>23</v>
       </c>
-      <c r="I236" s="4" t="s">
-        <v>5</v>
+      <c r="I236" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
@@ -7579,8 +7586,8 @@
       <c r="H237" s="4">
         <v>26</v>
       </c>
-      <c r="I237" s="4" t="s">
-        <v>4</v>
+      <c r="I237" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
@@ -7608,8 +7615,8 @@
       <c r="H238" s="4">
         <v>51</v>
       </c>
-      <c r="I238" s="4" t="s">
-        <v>4</v>
+      <c r="I238" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
@@ -7637,8 +7644,8 @@
       <c r="H239" s="4">
         <v>23</v>
       </c>
-      <c r="I239" s="4" t="s">
-        <v>4</v>
+      <c r="I239" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
@@ -7666,8 +7673,8 @@
       <c r="H240" s="4">
         <v>32</v>
       </c>
-      <c r="I240" s="4" t="s">
-        <v>4</v>
+      <c r="I240" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
@@ -7695,8 +7702,8 @@
       <c r="H241" s="4">
         <v>27</v>
       </c>
-      <c r="I241" s="4" t="s">
-        <v>5</v>
+      <c r="I241" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
@@ -7724,8 +7731,8 @@
       <c r="H242" s="4">
         <v>21</v>
       </c>
-      <c r="I242" s="4" t="s">
-        <v>5</v>
+      <c r="I242" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
@@ -7753,8 +7760,8 @@
       <c r="H243" s="4">
         <v>22</v>
       </c>
-      <c r="I243" s="4" t="s">
-        <v>5</v>
+      <c r="I243" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
@@ -7782,8 +7789,8 @@
       <c r="H244" s="4">
         <v>22</v>
       </c>
-      <c r="I244" s="4" t="s">
-        <v>4</v>
+      <c r="I244" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
@@ -7811,8 +7818,8 @@
       <c r="H245" s="4">
         <v>33</v>
       </c>
-      <c r="I245" s="4" t="s">
-        <v>4</v>
+      <c r="I245" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
@@ -7840,8 +7847,8 @@
       <c r="H246" s="4">
         <v>29</v>
       </c>
-      <c r="I246" s="4" t="s">
-        <v>5</v>
+      <c r="I246" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
@@ -7869,8 +7876,8 @@
       <c r="H247" s="4">
         <v>49</v>
       </c>
-      <c r="I247" s="4" t="s">
-        <v>4</v>
+      <c r="I247" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
@@ -7898,8 +7905,8 @@
       <c r="H248" s="4">
         <v>41</v>
       </c>
-      <c r="I248" s="4" t="s">
-        <v>5</v>
+      <c r="I248" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
@@ -7927,8 +7934,8 @@
       <c r="H249" s="4">
         <v>23</v>
       </c>
-      <c r="I249" s="4" t="s">
-        <v>5</v>
+      <c r="I249" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
@@ -7956,8 +7963,8 @@
       <c r="H250" s="4">
         <v>34</v>
       </c>
-      <c r="I250" s="4" t="s">
-        <v>5</v>
+      <c r="I250" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
@@ -7985,8 +7992,8 @@
       <c r="H251" s="4">
         <v>23</v>
       </c>
-      <c r="I251" s="4" t="s">
-        <v>5</v>
+      <c r="I251" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
@@ -8014,8 +8021,8 @@
       <c r="H252" s="4">
         <v>42</v>
       </c>
-      <c r="I252" s="4" t="s">
-        <v>5</v>
+      <c r="I252" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
@@ -8043,8 +8050,8 @@
       <c r="H253" s="4">
         <v>27</v>
       </c>
-      <c r="I253" s="4" t="s">
-        <v>5</v>
+      <c r="I253" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
@@ -8072,8 +8079,8 @@
       <c r="H254" s="4">
         <v>24</v>
       </c>
-      <c r="I254" s="4" t="s">
-        <v>5</v>
+      <c r="I254" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.2">
@@ -8101,8 +8108,8 @@
       <c r="H255" s="4">
         <v>25</v>
       </c>
-      <c r="I255" s="4" t="s">
-        <v>5</v>
+      <c r="I255" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.2">
@@ -8130,8 +8137,8 @@
       <c r="H256" s="4">
         <v>44</v>
       </c>
-      <c r="I256" s="4" t="s">
-        <v>4</v>
+      <c r="I256" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
@@ -8159,8 +8166,8 @@
       <c r="H257" s="4">
         <v>21</v>
       </c>
-      <c r="I257" s="4" t="s">
-        <v>4</v>
+      <c r="I257" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.2">
@@ -8188,8 +8195,8 @@
       <c r="H258" s="4">
         <v>30</v>
       </c>
-      <c r="I258" s="4" t="s">
-        <v>5</v>
+      <c r="I258" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
@@ -8217,8 +8224,8 @@
       <c r="H259" s="4">
         <v>25</v>
       </c>
-      <c r="I259" s="4" t="s">
-        <v>5</v>
+      <c r="I259" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
@@ -8246,8 +8253,8 @@
       <c r="H260" s="4">
         <v>24</v>
       </c>
-      <c r="I260" s="4" t="s">
-        <v>5</v>
+      <c r="I260" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
@@ -8275,8 +8282,8 @@
       <c r="H261" s="4">
         <v>51</v>
       </c>
-      <c r="I261" s="4" t="s">
-        <v>4</v>
+      <c r="I261" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.2">
@@ -8304,8 +8311,8 @@
       <c r="H262" s="4">
         <v>34</v>
       </c>
-      <c r="I262" s="4" t="s">
-        <v>5</v>
+      <c r="I262" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
@@ -8333,8 +8340,8 @@
       <c r="H263" s="4">
         <v>27</v>
       </c>
-      <c r="I263" s="4" t="s">
-        <v>4</v>
+      <c r="I263" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
@@ -8362,8 +8369,8 @@
       <c r="H264" s="4">
         <v>24</v>
       </c>
-      <c r="I264" s="4" t="s">
-        <v>5</v>
+      <c r="I264" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
@@ -8391,8 +8398,8 @@
       <c r="H265" s="4">
         <v>63</v>
       </c>
-      <c r="I265" s="4" t="s">
-        <v>5</v>
+      <c r="I265" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
@@ -8420,8 +8427,8 @@
       <c r="H266" s="4">
         <v>35</v>
       </c>
-      <c r="I266" s="4" t="s">
-        <v>4</v>
+      <c r="I266" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
@@ -8449,8 +8456,8 @@
       <c r="H267" s="4">
         <v>43</v>
       </c>
-      <c r="I267" s="4" t="s">
-        <v>5</v>
+      <c r="I267" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
@@ -8478,8 +8485,8 @@
       <c r="H268" s="4">
         <v>25</v>
       </c>
-      <c r="I268" s="4" t="s">
-        <v>4</v>
+      <c r="I268" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.2">
@@ -8507,8 +8514,8 @@
       <c r="H269" s="4">
         <v>24</v>
       </c>
-      <c r="I269" s="4" t="s">
-        <v>5</v>
+      <c r="I269" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.2">
@@ -8536,8 +8543,8 @@
       <c r="H270" s="4">
         <v>21</v>
       </c>
-      <c r="I270" s="4" t="s">
-        <v>5</v>
+      <c r="I270" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
@@ -8565,8 +8572,8 @@
       <c r="H271" s="4">
         <v>28</v>
       </c>
-      <c r="I271" s="4" t="s">
-        <v>4</v>
+      <c r="I271" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
@@ -8594,8 +8601,8 @@
       <c r="H272" s="4">
         <v>38</v>
       </c>
-      <c r="I272" s="4" t="s">
-        <v>4</v>
+      <c r="I272" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.2">
@@ -8623,8 +8630,8 @@
       <c r="H273" s="4">
         <v>21</v>
       </c>
-      <c r="I273" s="4" t="s">
-        <v>5</v>
+      <c r="I273" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.2">
@@ -8652,8 +8659,8 @@
       <c r="H274" s="4">
         <v>40</v>
       </c>
-      <c r="I274" s="4" t="s">
-        <v>5</v>
+      <c r="I274" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
@@ -8681,8 +8688,8 @@
       <c r="H275" s="4">
         <v>21</v>
       </c>
-      <c r="I275" s="4" t="s">
-        <v>5</v>
+      <c r="I275" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.2">
@@ -8710,8 +8717,8 @@
       <c r="H276" s="4">
         <v>52</v>
       </c>
-      <c r="I276" s="4" t="s">
-        <v>5</v>
+      <c r="I276" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.2">
@@ -8739,8 +8746,8 @@
       <c r="H277" s="4">
         <v>25</v>
       </c>
-      <c r="I277" s="4" t="s">
-        <v>5</v>
+      <c r="I277" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.2">
@@ -8768,8 +8775,8 @@
       <c r="H278" s="4">
         <v>29</v>
       </c>
-      <c r="I278" s="4" t="s">
-        <v>4</v>
+      <c r="I278" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.2">
@@ -8797,8 +8804,8 @@
       <c r="H279" s="4">
         <v>23</v>
       </c>
-      <c r="I279" s="4" t="s">
-        <v>5</v>
+      <c r="I279" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.2">
@@ -8826,8 +8833,8 @@
       <c r="H280" s="4">
         <v>57</v>
       </c>
-      <c r="I280" s="4" t="s">
-        <v>5</v>
+      <c r="I280" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.2">
@@ -8855,8 +8862,8 @@
       <c r="H281" s="4">
         <v>22</v>
       </c>
-      <c r="I281" s="4" t="s">
-        <v>5</v>
+      <c r="I281" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.2">
@@ -8884,8 +8891,8 @@
       <c r="H282" s="4">
         <v>28</v>
       </c>
-      <c r="I282" s="4" t="s">
-        <v>4</v>
+      <c r="I282" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.2">
@@ -8913,8 +8920,8 @@
       <c r="H283" s="4">
         <v>39</v>
       </c>
-      <c r="I283" s="4" t="s">
-        <v>5</v>
+      <c r="I283" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.2">
@@ -8942,8 +8949,8 @@
       <c r="H284" s="4">
         <v>37</v>
       </c>
-      <c r="I284" s="4" t="s">
-        <v>5</v>
+      <c r="I284" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.2">
@@ -8971,8 +8978,8 @@
       <c r="H285" s="4">
         <v>47</v>
       </c>
-      <c r="I285" s="4" t="s">
-        <v>4</v>
+      <c r="I285" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.2">
@@ -9000,8 +9007,8 @@
       <c r="H286" s="4">
         <v>52</v>
       </c>
-      <c r="I286" s="4" t="s">
-        <v>4</v>
+      <c r="I286" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
@@ -9029,8 +9036,8 @@
       <c r="H287" s="4">
         <v>51</v>
       </c>
-      <c r="I287" s="4" t="s">
-        <v>5</v>
+      <c r="I287" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.2">
@@ -9058,8 +9065,8 @@
       <c r="H288" s="4">
         <v>34</v>
       </c>
-      <c r="I288" s="4" t="s">
-        <v>5</v>
+      <c r="I288" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.2">
@@ -9087,8 +9094,8 @@
       <c r="H289" s="4">
         <v>29</v>
       </c>
-      <c r="I289" s="4" t="s">
-        <v>4</v>
+      <c r="I289" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
@@ -9116,8 +9123,8 @@
       <c r="H290" s="4">
         <v>26</v>
       </c>
-      <c r="I290" s="4" t="s">
-        <v>5</v>
+      <c r="I290" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
@@ -9145,8 +9152,8 @@
       <c r="H291" s="4">
         <v>33</v>
       </c>
-      <c r="I291" s="4" t="s">
-        <v>5</v>
+      <c r="I291" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
@@ -9174,8 +9181,8 @@
       <c r="H292" s="4">
         <v>21</v>
       </c>
-      <c r="I292" s="4" t="s">
-        <v>5</v>
+      <c r="I292" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
@@ -9203,8 +9210,8 @@
       <c r="H293" s="4">
         <v>25</v>
       </c>
-      <c r="I293" s="4" t="s">
-        <v>4</v>
+      <c r="I293" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
@@ -9232,8 +9239,8 @@
       <c r="H294" s="4">
         <v>31</v>
       </c>
-      <c r="I294" s="4" t="s">
-        <v>4</v>
+      <c r="I294" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.2">
@@ -9261,8 +9268,8 @@
       <c r="H295" s="4">
         <v>24</v>
       </c>
-      <c r="I295" s="4" t="s">
-        <v>4</v>
+      <c r="I295" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
@@ -9290,8 +9297,8 @@
       <c r="H296" s="4">
         <v>65</v>
       </c>
-      <c r="I296" s="4" t="s">
-        <v>5</v>
+      <c r="I296" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
@@ -9319,8 +9326,8 @@
       <c r="H297" s="4">
         <v>28</v>
       </c>
-      <c r="I297" s="4" t="s">
-        <v>5</v>
+      <c r="I297" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
@@ -9348,8 +9355,8 @@
       <c r="H298" s="4">
         <v>29</v>
       </c>
-      <c r="I298" s="4" t="s">
-        <v>4</v>
+      <c r="I298" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
@@ -9377,8 +9384,8 @@
       <c r="H299" s="4">
         <v>24</v>
       </c>
-      <c r="I299" s="4" t="s">
-        <v>5</v>
+      <c r="I299" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
@@ -9406,8 +9413,8 @@
       <c r="H300" s="4">
         <v>46</v>
       </c>
-      <c r="I300" s="4" t="s">
-        <v>4</v>
+      <c r="I300" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
@@ -9435,8 +9442,8 @@
       <c r="H301" s="4">
         <v>58</v>
       </c>
-      <c r="I301" s="4" t="s">
-        <v>5</v>
+      <c r="I301" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
@@ -9464,8 +9471,8 @@
       <c r="H302" s="4">
         <v>30</v>
       </c>
-      <c r="I302" s="4" t="s">
-        <v>4</v>
+      <c r="I302" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
@@ -9493,8 +9500,8 @@
       <c r="H303" s="4">
         <v>25</v>
       </c>
-      <c r="I303" s="4" t="s">
-        <v>4</v>
+      <c r="I303" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.2">
@@ -9522,8 +9529,8 @@
       <c r="H304" s="4">
         <v>35</v>
       </c>
-      <c r="I304" s="4" t="s">
-        <v>5</v>
+      <c r="I304" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.2">
@@ -9551,8 +9558,8 @@
       <c r="H305" s="4">
         <v>28</v>
       </c>
-      <c r="I305" s="4" t="s">
-        <v>4</v>
+      <c r="I305" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.2">
@@ -9580,8 +9587,8 @@
       <c r="H306" s="4">
         <v>37</v>
       </c>
-      <c r="I306" s="4" t="s">
-        <v>5</v>
+      <c r="I306" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.2">
@@ -9609,8 +9616,8 @@
       <c r="H307" s="4">
         <v>29</v>
       </c>
-      <c r="I307" s="4" t="s">
-        <v>5</v>
+      <c r="I307" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.2">
@@ -9638,8 +9645,8 @@
       <c r="H308" s="4">
         <v>47</v>
       </c>
-      <c r="I308" s="4" t="s">
-        <v>4</v>
+      <c r="I308" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.2">
@@ -9667,8 +9674,8 @@
       <c r="H309" s="4">
         <v>21</v>
       </c>
-      <c r="I309" s="4" t="s">
-        <v>5</v>
+      <c r="I309" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.2">
@@ -9696,8 +9703,8 @@
       <c r="H310" s="4">
         <v>25</v>
       </c>
-      <c r="I310" s="4" t="s">
-        <v>4</v>
+      <c r="I310" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.2">
@@ -9725,8 +9732,8 @@
       <c r="H311" s="4">
         <v>30</v>
       </c>
-      <c r="I311" s="4" t="s">
-        <v>4</v>
+      <c r="I311" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.2">
@@ -9754,8 +9761,8 @@
       <c r="H312" s="4">
         <v>41</v>
       </c>
-      <c r="I312" s="4" t="s">
-        <v>5</v>
+      <c r="I312" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.2">
@@ -9783,8 +9790,8 @@
       <c r="H313" s="4">
         <v>22</v>
       </c>
-      <c r="I313" s="4" t="s">
-        <v>5</v>
+      <c r="I313" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.2">
@@ -9812,8 +9819,8 @@
       <c r="H314" s="4">
         <v>27</v>
       </c>
-      <c r="I314" s="4" t="s">
-        <v>4</v>
+      <c r="I314" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.2">
@@ -9841,8 +9848,8 @@
       <c r="H315" s="4">
         <v>25</v>
       </c>
-      <c r="I315" s="4" t="s">
-        <v>5</v>
+      <c r="I315" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.2">
@@ -9870,8 +9877,8 @@
       <c r="H316" s="4">
         <v>43</v>
       </c>
-      <c r="I316" s="4" t="s">
-        <v>4</v>
+      <c r="I316" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.2">
@@ -9899,8 +9906,8 @@
       <c r="H317" s="4">
         <v>26</v>
       </c>
-      <c r="I317" s="4" t="s">
-        <v>5</v>
+      <c r="I317" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.2">
@@ -9928,8 +9935,8 @@
       <c r="H318" s="4">
         <v>30</v>
       </c>
-      <c r="I318" s="4" t="s">
-        <v>5</v>
+      <c r="I318" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.2">
@@ -9957,8 +9964,8 @@
       <c r="H319" s="4">
         <v>29</v>
       </c>
-      <c r="I319" s="4" t="s">
-        <v>4</v>
+      <c r="I319" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.2">
@@ -9986,8 +9993,8 @@
       <c r="H320" s="4">
         <v>28</v>
       </c>
-      <c r="I320" s="4" t="s">
-        <v>5</v>
+      <c r="I320" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.2">
@@ -10015,8 +10022,8 @@
       <c r="H321" s="4">
         <v>59</v>
       </c>
-      <c r="I321" s="4" t="s">
-        <v>4</v>
+      <c r="I321" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.2">
@@ -10044,8 +10051,8 @@
       <c r="H322" s="4">
         <v>31</v>
       </c>
-      <c r="I322" s="4" t="s">
-        <v>5</v>
+      <c r="I322" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.2">
@@ -10073,8 +10080,8 @@
       <c r="H323" s="4">
         <v>25</v>
       </c>
-      <c r="I323" s="4" t="s">
-        <v>4</v>
+      <c r="I323" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.2">
@@ -10102,8 +10109,8 @@
       <c r="H324" s="4">
         <v>36</v>
       </c>
-      <c r="I324" s="4" t="s">
-        <v>4</v>
+      <c r="I324" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.2">
@@ -10131,8 +10138,8 @@
       <c r="H325" s="4">
         <v>43</v>
       </c>
-      <c r="I325" s="4" t="s">
-        <v>4</v>
+      <c r="I325" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.2">
@@ -10160,8 +10167,8 @@
       <c r="H326" s="4">
         <v>21</v>
       </c>
-      <c r="I326" s="4" t="s">
-        <v>5</v>
+      <c r="I326" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.2">
@@ -10189,8 +10196,8 @@
       <c r="H327" s="4">
         <v>24</v>
       </c>
-      <c r="I327" s="4" t="s">
-        <v>5</v>
+      <c r="I327" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.2">
@@ -10218,8 +10225,8 @@
       <c r="H328" s="4">
         <v>30</v>
       </c>
-      <c r="I328" s="4" t="s">
-        <v>4</v>
+      <c r="I328" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.2">
@@ -10247,8 +10254,8 @@
       <c r="H329" s="4">
         <v>37</v>
       </c>
-      <c r="I329" s="4" t="s">
-        <v>5</v>
+      <c r="I329" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.2">
@@ -10276,8 +10283,8 @@
       <c r="H330" s="4">
         <v>23</v>
       </c>
-      <c r="I330" s="4" t="s">
-        <v>4</v>
+      <c r="I330" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.2">
@@ -10305,8 +10312,8 @@
       <c r="H331" s="4">
         <v>37</v>
       </c>
-      <c r="I331" s="4" t="s">
-        <v>5</v>
+      <c r="I331" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.2">
@@ -10334,8 +10341,8 @@
       <c r="H332" s="4">
         <v>46</v>
       </c>
-      <c r="I332" s="4" t="s">
-        <v>5</v>
+      <c r="I332" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.2">
@@ -10363,8 +10370,8 @@
       <c r="H333" s="4">
         <v>25</v>
       </c>
-      <c r="I333" s="4" t="s">
-        <v>5</v>
+      <c r="I333" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.2">
@@ -10392,8 +10399,8 @@
       <c r="H334" s="4">
         <v>41</v>
       </c>
-      <c r="I334" s="4" t="s">
-        <v>4</v>
+      <c r="I334" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.2">
@@ -10421,8 +10428,8 @@
       <c r="H335" s="4">
         <v>44</v>
       </c>
-      <c r="I335" s="4" t="s">
-        <v>5</v>
+      <c r="I335" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.2">
@@ -10450,8 +10457,8 @@
       <c r="H336" s="4">
         <v>22</v>
       </c>
-      <c r="I336" s="4" t="s">
-        <v>5</v>
+      <c r="I336" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.2">
@@ -10479,8 +10486,8 @@
       <c r="H337" s="4">
         <v>26</v>
       </c>
-      <c r="I337" s="4" t="s">
-        <v>5</v>
+      <c r="I337" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.2">
@@ -10508,8 +10515,8 @@
       <c r="H338" s="4">
         <v>44</v>
       </c>
-      <c r="I338" s="4" t="s">
-        <v>5</v>
+      <c r="I338" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.2">
@@ -10537,8 +10544,8 @@
       <c r="H339" s="4">
         <v>44</v>
       </c>
-      <c r="I339" s="4" t="s">
-        <v>4</v>
+      <c r="I339" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.2">
@@ -10566,8 +10573,8 @@
       <c r="H340" s="4">
         <v>33</v>
       </c>
-      <c r="I340" s="4" t="s">
-        <v>4</v>
+      <c r="I340" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.2">
@@ -10595,8 +10602,8 @@
       <c r="H341" s="4">
         <v>41</v>
       </c>
-      <c r="I341" s="4" t="s">
-        <v>4</v>
+      <c r="I341" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.2">
@@ -10624,8 +10631,8 @@
       <c r="H342" s="4">
         <v>22</v>
       </c>
-      <c r="I342" s="4" t="s">
-        <v>5</v>
+      <c r="I342" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.2">
@@ -10653,8 +10660,8 @@
       <c r="H343" s="4">
         <v>36</v>
       </c>
-      <c r="I343" s="4" t="s">
-        <v>5</v>
+      <c r="I343" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.2">
@@ -10682,8 +10689,8 @@
       <c r="H344" s="4">
         <v>22</v>
       </c>
-      <c r="I344" s="4" t="s">
-        <v>5</v>
+      <c r="I344" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.2">
@@ -10711,8 +10718,8 @@
       <c r="H345" s="4">
         <v>33</v>
       </c>
-      <c r="I345" s="4" t="s">
-        <v>5</v>
+      <c r="I345" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.2">
@@ -10740,8 +10747,8 @@
       <c r="H346" s="4">
         <v>57</v>
       </c>
-      <c r="I346" s="4" t="s">
-        <v>5</v>
+      <c r="I346" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.2">
@@ -10769,8 +10776,8 @@
       <c r="H347" s="4">
         <v>49</v>
       </c>
-      <c r="I347" s="4" t="s">
-        <v>5</v>
+      <c r="I347" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.2">
@@ -10798,8 +10805,8 @@
       <c r="H348" s="4">
         <v>22</v>
       </c>
-      <c r="I348" s="4" t="s">
-        <v>5</v>
+      <c r="I348" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.2">
@@ -10827,8 +10834,8 @@
       <c r="H349" s="4">
         <v>23</v>
       </c>
-      <c r="I349" s="4" t="s">
-        <v>5</v>
+      <c r="I349" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.2">
@@ -10856,8 +10863,8 @@
       <c r="H350" s="4">
         <v>26</v>
       </c>
-      <c r="I350" s="4" t="s">
-        <v>5</v>
+      <c r="I350" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.2">
@@ -10885,8 +10892,8 @@
       <c r="H351" s="4">
         <v>37</v>
       </c>
-      <c r="I351" s="4" t="s">
-        <v>4</v>
+      <c r="I351" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.2">
@@ -10914,8 +10921,8 @@
       <c r="H352" s="4">
         <v>29</v>
       </c>
-      <c r="I352" s="4" t="s">
-        <v>5</v>
+      <c r="I352" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.2">
@@ -10943,8 +10950,8 @@
       <c r="H353" s="4">
         <v>30</v>
       </c>
-      <c r="I353" s="4" t="s">
-        <v>5</v>
+      <c r="I353" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.2">
@@ -10972,8 +10979,8 @@
       <c r="H354" s="4">
         <v>46</v>
       </c>
-      <c r="I354" s="4" t="s">
-        <v>5</v>
+      <c r="I354" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.2">
@@ -11001,8 +11008,8 @@
       <c r="H355" s="4">
         <v>24</v>
       </c>
-      <c r="I355" s="4" t="s">
-        <v>5</v>
+      <c r="I355" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.2">
@@ -11030,8 +11037,8 @@
       <c r="H356" s="4">
         <v>21</v>
       </c>
-      <c r="I356" s="4" t="s">
-        <v>5</v>
+      <c r="I356" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.2">
@@ -11059,8 +11066,8 @@
       <c r="H357" s="4">
         <v>49</v>
       </c>
-      <c r="I357" s="4" t="s">
-        <v>4</v>
+      <c r="I357" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.2">
@@ -11088,8 +11095,8 @@
       <c r="H358" s="4">
         <v>28</v>
       </c>
-      <c r="I358" s="4" t="s">
-        <v>4</v>
+      <c r="I358" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.2">
@@ -11117,8 +11124,8 @@
       <c r="H359" s="4">
         <v>44</v>
       </c>
-      <c r="I359" s="4" t="s">
-        <v>4</v>
+      <c r="I359" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.2">
@@ -11146,8 +11153,8 @@
       <c r="H360" s="4">
         <v>48</v>
       </c>
-      <c r="I360" s="4" t="s">
-        <v>5</v>
+      <c r="I360" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.2">
@@ -11175,8 +11182,8 @@
       <c r="H361" s="4">
         <v>29</v>
       </c>
-      <c r="I361" s="4" t="s">
-        <v>4</v>
+      <c r="I361" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.2">
@@ -11204,8 +11211,8 @@
       <c r="H362" s="4">
         <v>29</v>
       </c>
-      <c r="I362" s="4" t="s">
-        <v>4</v>
+      <c r="I362" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.2">
@@ -11233,8 +11240,8 @@
       <c r="H363" s="4">
         <v>63</v>
       </c>
-      <c r="I363" s="4" t="s">
-        <v>5</v>
+      <c r="I363" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.2">
@@ -11262,8 +11269,8 @@
       <c r="H364" s="4">
         <v>65</v>
       </c>
-      <c r="I364" s="4" t="s">
-        <v>5</v>
+      <c r="I364" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.2">
@@ -11291,8 +11298,8 @@
       <c r="H365" s="4">
         <v>67</v>
       </c>
-      <c r="I365" s="4" t="s">
-        <v>4</v>
+      <c r="I365" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.2">
@@ -11320,8 +11327,8 @@
       <c r="H366" s="4">
         <v>30</v>
       </c>
-      <c r="I366" s="4" t="s">
-        <v>5</v>
+      <c r="I366" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.2">
@@ -11349,8 +11356,8 @@
       <c r="H367" s="4">
         <v>30</v>
       </c>
-      <c r="I367" s="4" t="s">
-        <v>5</v>
+      <c r="I367" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.2">
@@ -11378,8 +11385,8 @@
       <c r="H368" s="4">
         <v>29</v>
       </c>
-      <c r="I368" s="4" t="s">
-        <v>4</v>
+      <c r="I368" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.2">
@@ -11407,8 +11414,8 @@
       <c r="H369" s="4">
         <v>21</v>
       </c>
-      <c r="I369" s="4" t="s">
-        <v>5</v>
+      <c r="I369" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.2">
@@ -11436,8 +11443,8 @@
       <c r="H370" s="4">
         <v>22</v>
       </c>
-      <c r="I370" s="4" t="s">
-        <v>5</v>
+      <c r="I370" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.2">
@@ -11465,8 +11472,8 @@
       <c r="H371" s="4">
         <v>45</v>
       </c>
-      <c r="I371" s="4" t="s">
-        <v>4</v>
+      <c r="I371" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.2">
@@ -11494,8 +11501,8 @@
       <c r="H372" s="4">
         <v>25</v>
       </c>
-      <c r="I372" s="4" t="s">
-        <v>4</v>
+      <c r="I372" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.2">
@@ -11523,8 +11530,8 @@
       <c r="H373" s="4">
         <v>21</v>
       </c>
-      <c r="I373" s="4" t="s">
-        <v>5</v>
+      <c r="I373" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.2">
@@ -11552,8 +11559,8 @@
       <c r="H374" s="4">
         <v>21</v>
       </c>
-      <c r="I374" s="4" t="s">
-        <v>5</v>
+      <c r="I374" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.2">
@@ -11581,8 +11588,8 @@
       <c r="H375" s="4">
         <v>25</v>
       </c>
-      <c r="I375" s="4" t="s">
-        <v>5</v>
+      <c r="I375" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.2">
@@ -11610,8 +11617,8 @@
       <c r="H376" s="4">
         <v>28</v>
       </c>
-      <c r="I376" s="4" t="s">
-        <v>5</v>
+      <c r="I376" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.2">
@@ -11639,8 +11646,8 @@
       <c r="H377" s="4">
         <v>58</v>
       </c>
-      <c r="I377" s="4" t="s">
-        <v>4</v>
+      <c r="I377" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.2">
@@ -11668,8 +11675,8 @@
       <c r="H378" s="4">
         <v>22</v>
       </c>
-      <c r="I378" s="4" t="s">
-        <v>5</v>
+      <c r="I378" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.2">
@@ -11697,8 +11704,8 @@
       <c r="H379" s="4">
         <v>22</v>
       </c>
-      <c r="I379" s="4" t="s">
-        <v>5</v>
+      <c r="I379" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.2">
@@ -11726,8 +11733,8 @@
       <c r="H380" s="4">
         <v>32</v>
       </c>
-      <c r="I380" s="4" t="s">
-        <v>4</v>
+      <c r="I380" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.2">
@@ -11755,8 +11762,8 @@
       <c r="H381" s="4">
         <v>35</v>
       </c>
-      <c r="I381" s="4" t="s">
-        <v>5</v>
+      <c r="I381" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.2">
@@ -11784,8 +11791,8 @@
       <c r="H382" s="4">
         <v>24</v>
       </c>
-      <c r="I382" s="4" t="s">
-        <v>5</v>
+      <c r="I382" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.2">
@@ -11813,8 +11820,8 @@
       <c r="H383" s="4">
         <v>22</v>
       </c>
-      <c r="I383" s="4" t="s">
-        <v>5</v>
+      <c r="I383" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.2">
@@ -11842,8 +11849,8 @@
       <c r="H384" s="4">
         <v>21</v>
       </c>
-      <c r="I384" s="4" t="s">
-        <v>5</v>
+      <c r="I384" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.2">
@@ -11871,8 +11878,8 @@
       <c r="H385" s="4">
         <v>25</v>
       </c>
-      <c r="I385" s="4" t="s">
-        <v>5</v>
+      <c r="I385" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.2">
@@ -11900,8 +11907,8 @@
       <c r="H386" s="4">
         <v>25</v>
       </c>
-      <c r="I386" s="4" t="s">
-        <v>5</v>
+      <c r="I386" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.2">
@@ -11929,8 +11936,8 @@
       <c r="H387" s="4">
         <v>24</v>
       </c>
-      <c r="I387" s="4" t="s">
-        <v>5</v>
+      <c r="I387" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.2">
@@ -11958,8 +11965,8 @@
       <c r="H388" s="4">
         <v>35</v>
       </c>
-      <c r="I388" s="4" t="s">
-        <v>4</v>
+      <c r="I388" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.2">
@@ -11987,8 +11994,8 @@
       <c r="H389" s="4">
         <v>45</v>
       </c>
-      <c r="I389" s="4" t="s">
-        <v>4</v>
+      <c r="I389" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.2">
@@ -12016,8 +12023,8 @@
       <c r="H390" s="4">
         <v>58</v>
       </c>
-      <c r="I390" s="4" t="s">
-        <v>4</v>
+      <c r="I390" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.2">
@@ -12045,8 +12052,8 @@
       <c r="H391" s="4">
         <v>28</v>
       </c>
-      <c r="I391" s="4" t="s">
-        <v>5</v>
+      <c r="I391" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.2">
@@ -12074,8 +12081,8 @@
       <c r="H392" s="4">
         <v>42</v>
       </c>
-      <c r="I392" s="4" t="s">
-        <v>5</v>
+      <c r="I392" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.2">
@@ -12103,8 +12110,8 @@
       <c r="H393" s="4">
         <v>27</v>
       </c>
-      <c r="I393" s="4" t="s">
-        <v>4</v>
+      <c r="I393" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.2">
@@ -12132,8 +12139,8 @@
       <c r="H394" s="4">
         <v>21</v>
       </c>
-      <c r="I394" s="4" t="s">
-        <v>5</v>
+      <c r="I394" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.2">
@@ -12161,8 +12168,8 @@
       <c r="H395" s="4">
         <v>37</v>
       </c>
-      <c r="I395" s="4" t="s">
-        <v>5</v>
+      <c r="I395" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.2">
@@ -12190,8 +12197,8 @@
       <c r="H396" s="4">
         <v>31</v>
       </c>
-      <c r="I396" s="4" t="s">
-        <v>4</v>
+      <c r="I396" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.2">
@@ -12219,8 +12226,8 @@
       <c r="H397" s="4">
         <v>25</v>
       </c>
-      <c r="I397" s="4" t="s">
-        <v>5</v>
+      <c r="I397" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.2">
@@ -12248,8 +12255,8 @@
       <c r="H398" s="4">
         <v>39</v>
       </c>
-      <c r="I398" s="4" t="s">
-        <v>5</v>
+      <c r="I398" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.2">
@@ -12277,8 +12284,8 @@
       <c r="H399" s="4">
         <v>22</v>
       </c>
-      <c r="I399" s="4" t="s">
-        <v>4</v>
+      <c r="I399" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.2">
@@ -12306,8 +12313,8 @@
       <c r="H400" s="4">
         <v>25</v>
       </c>
-      <c r="I400" s="4" t="s">
-        <v>5</v>
+      <c r="I400" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.2">
@@ -12335,8 +12342,8 @@
       <c r="H401" s="4">
         <v>25</v>
       </c>
-      <c r="I401" s="4" t="s">
-        <v>4</v>
+      <c r="I401" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.2">
@@ -12364,8 +12371,8 @@
       <c r="H402" s="4">
         <v>31</v>
       </c>
-      <c r="I402" s="4" t="s">
-        <v>4</v>
+      <c r="I402" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.2">
@@ -12393,8 +12400,8 @@
       <c r="H403" s="4">
         <v>55</v>
       </c>
-      <c r="I403" s="4" t="s">
-        <v>5</v>
+      <c r="I403" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.2">
@@ -12422,8 +12429,8 @@
       <c r="H404" s="4">
         <v>35</v>
       </c>
-      <c r="I404" s="4" t="s">
-        <v>4</v>
+      <c r="I404" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.2">
@@ -12451,8 +12458,8 @@
       <c r="H405" s="4">
         <v>38</v>
       </c>
-      <c r="I405" s="4" t="s">
-        <v>5</v>
+      <c r="I405" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.2">
@@ -12480,8 +12487,8 @@
       <c r="H406" s="4">
         <v>41</v>
       </c>
-      <c r="I406" s="4" t="s">
-        <v>4</v>
+      <c r="I406" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.2">
@@ -12509,8 +12516,8 @@
       <c r="H407" s="4">
         <v>26</v>
       </c>
-      <c r="I407" s="4" t="s">
-        <v>5</v>
+      <c r="I407" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.2">
@@ -12538,8 +12545,8 @@
       <c r="H408" s="4">
         <v>46</v>
       </c>
-      <c r="I408" s="4" t="s">
-        <v>4</v>
+      <c r="I408" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.2">
@@ -12567,8 +12574,8 @@
       <c r="H409" s="4">
         <v>25</v>
       </c>
-      <c r="I409" s="4" t="s">
-        <v>5</v>
+      <c r="I409" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.2">
@@ -12596,8 +12603,8 @@
       <c r="H410" s="4">
         <v>39</v>
       </c>
-      <c r="I410" s="4" t="s">
-        <v>4</v>
+      <c r="I410" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.2">
@@ -12625,8 +12632,8 @@
       <c r="H411" s="4">
         <v>28</v>
       </c>
-      <c r="I411" s="4" t="s">
-        <v>4</v>
+      <c r="I411" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.2">
@@ -12654,8 +12661,8 @@
       <c r="H412" s="4">
         <v>28</v>
       </c>
-      <c r="I412" s="4" t="s">
-        <v>5</v>
+      <c r="I412" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.2">
@@ -12683,8 +12690,8 @@
       <c r="H413" s="4">
         <v>25</v>
       </c>
-      <c r="I413" s="4" t="s">
-        <v>5</v>
+      <c r="I413" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.2">
@@ -12712,8 +12719,8 @@
       <c r="H414" s="4">
         <v>22</v>
       </c>
-      <c r="I414" s="4" t="s">
-        <v>5</v>
+      <c r="I414" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.2">
@@ -12741,8 +12748,8 @@
       <c r="H415" s="4">
         <v>21</v>
       </c>
-      <c r="I415" s="4" t="s">
-        <v>5</v>
+      <c r="I415" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.2">
@@ -12770,8 +12777,8 @@
       <c r="H416" s="4">
         <v>21</v>
       </c>
-      <c r="I416" s="4" t="s">
-        <v>4</v>
+      <c r="I416" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.2">
@@ -12799,8 +12806,8 @@
       <c r="H417" s="4">
         <v>22</v>
       </c>
-      <c r="I417" s="4" t="s">
-        <v>4</v>
+      <c r="I417" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.2">
@@ -12828,8 +12835,8 @@
       <c r="H418" s="4">
         <v>22</v>
       </c>
-      <c r="I418" s="4" t="s">
-        <v>5</v>
+      <c r="I418" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.2">
@@ -12857,8 +12864,8 @@
       <c r="H419" s="4">
         <v>37</v>
       </c>
-      <c r="I419" s="4" t="s">
-        <v>4</v>
+      <c r="I419" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.2">
@@ -12886,8 +12893,8 @@
       <c r="H420" s="4">
         <v>27</v>
       </c>
-      <c r="I420" s="4" t="s">
-        <v>5</v>
+      <c r="I420" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.2">
@@ -12915,8 +12922,8 @@
       <c r="H421" s="4">
         <v>28</v>
       </c>
-      <c r="I421" s="4" t="s">
-        <v>4</v>
+      <c r="I421" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.2">
@@ -12944,8 +12951,8 @@
       <c r="H422" s="4">
         <v>26</v>
       </c>
-      <c r="I422" s="4" t="s">
-        <v>5</v>
+      <c r="I422" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.2">
@@ -12973,8 +12980,8 @@
       <c r="H423" s="4">
         <v>21</v>
       </c>
-      <c r="I423" s="4" t="s">
-        <v>5</v>
+      <c r="I423" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.2">
@@ -13002,8 +13009,8 @@
       <c r="H424" s="4">
         <v>21</v>
       </c>
-      <c r="I424" s="4" t="s">
-        <v>5</v>
+      <c r="I424" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.2">
@@ -13031,8 +13038,8 @@
       <c r="H425" s="4">
         <v>21</v>
       </c>
-      <c r="I425" s="4" t="s">
-        <v>5</v>
+      <c r="I425" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.2">
@@ -13060,8 +13067,8 @@
       <c r="H426" s="4">
         <v>36</v>
       </c>
-      <c r="I426" s="4" t="s">
-        <v>4</v>
+      <c r="I426" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.2">
@@ -13089,8 +13096,8 @@
       <c r="H427" s="4">
         <v>31</v>
       </c>
-      <c r="I427" s="4" t="s">
-        <v>4</v>
+      <c r="I427" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.2">
@@ -13118,8 +13125,8 @@
       <c r="H428" s="4">
         <v>25</v>
       </c>
-      <c r="I428" s="4" t="s">
-        <v>5</v>
+      <c r="I428" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.2">
@@ -13147,8 +13154,8 @@
       <c r="H429" s="4">
         <v>38</v>
       </c>
-      <c r="I429" s="4" t="s">
-        <v>4</v>
+      <c r="I429" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.2">
@@ -13176,8 +13183,8 @@
       <c r="H430" s="4">
         <v>26</v>
       </c>
-      <c r="I430" s="4" t="s">
-        <v>5</v>
+      <c r="I430" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.2">
@@ -13205,8 +13212,8 @@
       <c r="H431" s="4">
         <v>43</v>
       </c>
-      <c r="I431" s="4" t="s">
-        <v>4</v>
+      <c r="I431" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.2">
@@ -13234,8 +13241,8 @@
       <c r="H432" s="4">
         <v>23</v>
       </c>
-      <c r="I432" s="4" t="s">
-        <v>5</v>
+      <c r="I432" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.2">
@@ -13263,8 +13270,8 @@
       <c r="H433" s="4">
         <v>38</v>
       </c>
-      <c r="I433" s="4" t="s">
-        <v>5</v>
+      <c r="I433" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.2">
@@ -13292,8 +13299,8 @@
       <c r="H434" s="4">
         <v>22</v>
       </c>
-      <c r="I434" s="4" t="s">
-        <v>5</v>
+      <c r="I434" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.2">
@@ -13321,8 +13328,8 @@
       <c r="H435" s="4">
         <v>29</v>
       </c>
-      <c r="I435" s="4" t="s">
-        <v>5</v>
+      <c r="I435" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.2">
@@ -13350,8 +13357,8 @@
       <c r="H436" s="4">
         <v>36</v>
       </c>
-      <c r="I436" s="4" t="s">
-        <v>5</v>
+      <c r="I436" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.2">
@@ -13379,8 +13386,8 @@
       <c r="H437" s="4">
         <v>29</v>
       </c>
-      <c r="I437" s="4" t="s">
-        <v>4</v>
+      <c r="I437" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.2">
@@ -13408,8 +13415,8 @@
       <c r="H438" s="4">
         <v>41</v>
       </c>
-      <c r="I438" s="4" t="s">
-        <v>5</v>
+      <c r="I438" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.2">
@@ -13437,8 +13444,8 @@
       <c r="H439" s="4">
         <v>28</v>
       </c>
-      <c r="I439" s="4" t="s">
-        <v>5</v>
+      <c r="I439" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.2">
@@ -13466,8 +13473,8 @@
       <c r="H440" s="4">
         <v>21</v>
       </c>
-      <c r="I440" s="4" t="s">
-        <v>5</v>
+      <c r="I440" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.2">
@@ -13495,8 +13502,8 @@
       <c r="H441" s="4">
         <v>31</v>
       </c>
-      <c r="I441" s="4" t="s">
-        <v>5</v>
+      <c r="I441" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.2">
@@ -13524,8 +13531,8 @@
       <c r="H442" s="4">
         <v>41</v>
       </c>
-      <c r="I442" s="4" t="s">
-        <v>4</v>
+      <c r="I442" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.2">
@@ -13553,8 +13560,8 @@
       <c r="H443" s="4">
         <v>22</v>
       </c>
-      <c r="I443" s="4" t="s">
-        <v>5</v>
+      <c r="I443" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.2">
@@ -13582,8 +13589,8 @@
       <c r="H444" s="4">
         <v>24</v>
       </c>
-      <c r="I444" s="4" t="s">
-        <v>5</v>
+      <c r="I444" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.2">
@@ -13611,8 +13618,8 @@
       <c r="H445" s="4">
         <v>33</v>
       </c>
-      <c r="I445" s="4" t="s">
-        <v>4</v>
+      <c r="I445" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.2">
@@ -13640,8 +13647,8 @@
       <c r="H446" s="4">
         <v>30</v>
       </c>
-      <c r="I446" s="4" t="s">
-        <v>4</v>
+      <c r="I446" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.2">
@@ -13669,8 +13676,8 @@
       <c r="H447" s="4">
         <v>25</v>
       </c>
-      <c r="I447" s="4" t="s">
-        <v>4</v>
+      <c r="I447" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.2">
@@ -13698,8 +13705,8 @@
       <c r="H448" s="4">
         <v>28</v>
       </c>
-      <c r="I448" s="4" t="s">
-        <v>5</v>
+      <c r="I448" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.2">
@@ -13727,8 +13734,8 @@
       <c r="H449" s="4">
         <v>26</v>
       </c>
-      <c r="I449" s="4" t="s">
-        <v>5</v>
+      <c r="I449" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.2">
@@ -13756,8 +13763,8 @@
       <c r="H450" s="4">
         <v>22</v>
       </c>
-      <c r="I450" s="4" t="s">
-        <v>4</v>
+      <c r="I450" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.2">
@@ -13785,8 +13792,8 @@
       <c r="H451" s="4">
         <v>26</v>
       </c>
-      <c r="I451" s="4" t="s">
-        <v>5</v>
+      <c r="I451" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.2">
@@ -13814,8 +13821,8 @@
       <c r="H452" s="4">
         <v>23</v>
       </c>
-      <c r="I452" s="4" t="s">
-        <v>5</v>
+      <c r="I452" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.2">
@@ -13843,8 +13850,8 @@
       <c r="H453" s="4">
         <v>23</v>
       </c>
-      <c r="I453" s="4" t="s">
-        <v>4</v>
+      <c r="I453" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.2">
@@ -13872,8 +13879,8 @@
       <c r="H454" s="4">
         <v>25</v>
       </c>
-      <c r="I454" s="4" t="s">
-        <v>5</v>
+      <c r="I454" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.2">
@@ -13901,8 +13908,8 @@
       <c r="H455" s="4">
         <v>72</v>
       </c>
-      <c r="I455" s="4" t="s">
-        <v>5</v>
+      <c r="I455" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.2">
@@ -13930,8 +13937,8 @@
       <c r="H456" s="4">
         <v>24</v>
       </c>
-      <c r="I456" s="4" t="s">
-        <v>5</v>
+      <c r="I456" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.2">
@@ -13959,8 +13966,8 @@
       <c r="H457" s="4">
         <v>38</v>
       </c>
-      <c r="I457" s="4" t="s">
-        <v>4</v>
+      <c r="I457" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.2">
@@ -13988,8 +13995,8 @@
       <c r="H458" s="4">
         <v>62</v>
       </c>
-      <c r="I458" s="4" t="s">
-        <v>5</v>
+      <c r="I458" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.2">
@@ -14017,8 +14024,8 @@
       <c r="H459" s="4">
         <v>24</v>
       </c>
-      <c r="I459" s="4" t="s">
-        <v>5</v>
+      <c r="I459" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.2">
@@ -14046,8 +14053,8 @@
       <c r="H460" s="4">
         <v>51</v>
       </c>
-      <c r="I460" s="4" t="s">
-        <v>4</v>
+      <c r="I460" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.2">
@@ -14075,8 +14082,8 @@
       <c r="H461" s="4">
         <v>81</v>
       </c>
-      <c r="I461" s="4" t="s">
-        <v>5</v>
+      <c r="I461" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.2">
@@ -14104,8 +14111,8 @@
       <c r="H462" s="4">
         <v>48</v>
       </c>
-      <c r="I462" s="4" t="s">
-        <v>5</v>
+      <c r="I462" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="463" spans="1:9" x14ac:dyDescent="0.2">
@@ -14133,8 +14140,8 @@
       <c r="H463" s="4">
         <v>26</v>
       </c>
-      <c r="I463" s="4" t="s">
-        <v>5</v>
+      <c r="I463" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="464" spans="1:9" x14ac:dyDescent="0.2">
@@ -14162,8 +14169,8 @@
       <c r="H464" s="4">
         <v>39</v>
       </c>
-      <c r="I464" s="4" t="s">
-        <v>5</v>
+      <c r="I464" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="465" spans="1:9" x14ac:dyDescent="0.2">
@@ -14191,8 +14198,8 @@
       <c r="H465" s="4">
         <v>37</v>
       </c>
-      <c r="I465" s="4" t="s">
-        <v>5</v>
+      <c r="I465" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.2">
@@ -14220,8 +14227,8 @@
       <c r="H466" s="4">
         <v>34</v>
       </c>
-      <c r="I466" s="4" t="s">
-        <v>5</v>
+      <c r="I466" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.2">
@@ -14249,8 +14256,8 @@
       <c r="H467" s="4">
         <v>21</v>
       </c>
-      <c r="I467" s="4" t="s">
-        <v>5</v>
+      <c r="I467" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.2">
@@ -14278,8 +14285,8 @@
       <c r="H468" s="4">
         <v>22</v>
       </c>
-      <c r="I468" s="4" t="s">
-        <v>5</v>
+      <c r="I468" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.2">
@@ -14307,8 +14314,8 @@
       <c r="H469" s="4">
         <v>25</v>
       </c>
-      <c r="I469" s="4" t="s">
-        <v>5</v>
+      <c r="I469" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.2">
@@ -14336,8 +14343,8 @@
       <c r="H470" s="4">
         <v>38</v>
       </c>
-      <c r="I470" s="4" t="s">
-        <v>4</v>
+      <c r="I470" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.2">
@@ -14365,8 +14372,8 @@
       <c r="H471" s="4">
         <v>27</v>
       </c>
-      <c r="I471" s="4" t="s">
-        <v>5</v>
+      <c r="I471" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.2">
@@ -14394,8 +14401,8 @@
       <c r="H472" s="4">
         <v>28</v>
       </c>
-      <c r="I472" s="4" t="s">
-        <v>5</v>
+      <c r="I472" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.2">
@@ -14423,8 +14430,8 @@
       <c r="H473" s="4">
         <v>22</v>
       </c>
-      <c r="I473" s="4" t="s">
-        <v>5</v>
+      <c r="I473" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.2">
@@ -14452,8 +14459,8 @@
       <c r="H474" s="4">
         <v>22</v>
       </c>
-      <c r="I474" s="4" t="s">
-        <v>5</v>
+      <c r="I474" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.2">
@@ -14481,8 +14488,8 @@
       <c r="H475" s="4">
         <v>50</v>
       </c>
-      <c r="I475" s="4" t="s">
-        <v>5</v>
+      <c r="I475" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="476" spans="1:9" x14ac:dyDescent="0.2">
@@ -14510,8 +14517,8 @@
       <c r="H476" s="4">
         <v>24</v>
       </c>
-      <c r="I476" s="4" t="s">
-        <v>5</v>
+      <c r="I476" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.2">
@@ -14539,8 +14546,8 @@
       <c r="H477" s="4">
         <v>59</v>
       </c>
-      <c r="I477" s="4" t="s">
-        <v>5</v>
+      <c r="I477" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.2">
@@ -14568,8 +14575,8 @@
       <c r="H478" s="4">
         <v>29</v>
       </c>
-      <c r="I478" s="4" t="s">
-        <v>4</v>
+      <c r="I478" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.2">
@@ -14597,8 +14604,8 @@
       <c r="H479" s="4">
         <v>31</v>
       </c>
-      <c r="I479" s="4" t="s">
-        <v>5</v>
+      <c r="I479" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="480" spans="1:9" x14ac:dyDescent="0.2">
@@ -14626,8 +14633,8 @@
       <c r="H480" s="4">
         <v>39</v>
       </c>
-      <c r="I480" s="4" t="s">
-        <v>5</v>
+      <c r="I480" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="481" spans="1:9" x14ac:dyDescent="0.2">
@@ -14655,8 +14662,8 @@
       <c r="H481" s="4">
         <v>63</v>
       </c>
-      <c r="I481" s="4" t="s">
-        <v>5</v>
+      <c r="I481" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="482" spans="1:9" x14ac:dyDescent="0.2">
@@ -14684,8 +14691,8 @@
       <c r="H482" s="4">
         <v>35</v>
       </c>
-      <c r="I482" s="4" t="s">
-        <v>4</v>
+      <c r="I482" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="483" spans="1:9" x14ac:dyDescent="0.2">
@@ -14713,8 +14720,8 @@
       <c r="H483" s="4">
         <v>29</v>
       </c>
-      <c r="I483" s="4" t="s">
-        <v>5</v>
+      <c r="I483" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.2">
@@ -14742,8 +14749,8 @@
       <c r="H484" s="4">
         <v>28</v>
       </c>
-      <c r="I484" s="4" t="s">
-        <v>5</v>
+      <c r="I484" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="485" spans="1:9" x14ac:dyDescent="0.2">
@@ -14771,8 +14778,8 @@
       <c r="H485" s="4">
         <v>23</v>
       </c>
-      <c r="I485" s="4" t="s">
-        <v>5</v>
+      <c r="I485" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="486" spans="1:9" x14ac:dyDescent="0.2">
@@ -14800,8 +14807,8 @@
       <c r="H486" s="4">
         <v>31</v>
       </c>
-      <c r="I486" s="4" t="s">
-        <v>4</v>
+      <c r="I486" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="487" spans="1:9" x14ac:dyDescent="0.2">
@@ -14829,8 +14836,8 @@
       <c r="H487" s="4">
         <v>24</v>
       </c>
-      <c r="I487" s="4" t="s">
-        <v>4</v>
+      <c r="I487" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="488" spans="1:9" x14ac:dyDescent="0.2">
@@ -14858,8 +14865,8 @@
       <c r="H488" s="4">
         <v>21</v>
       </c>
-      <c r="I488" s="4" t="s">
-        <v>5</v>
+      <c r="I488" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.2">
@@ -14887,8 +14894,8 @@
       <c r="H489" s="4">
         <v>58</v>
       </c>
-      <c r="I489" s="4" t="s">
-        <v>5</v>
+      <c r="I489" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="490" spans="1:9" x14ac:dyDescent="0.2">
@@ -14916,8 +14923,8 @@
       <c r="H490" s="4">
         <v>28</v>
       </c>
-      <c r="I490" s="4" t="s">
-        <v>5</v>
+      <c r="I490" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="491" spans="1:9" x14ac:dyDescent="0.2">
@@ -14945,8 +14952,8 @@
       <c r="H491" s="4">
         <v>67</v>
       </c>
-      <c r="I491" s="4" t="s">
-        <v>5</v>
+      <c r="I491" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="492" spans="1:9" x14ac:dyDescent="0.2">
@@ -14974,8 +14981,8 @@
       <c r="H492" s="4">
         <v>24</v>
       </c>
-      <c r="I492" s="4" t="s">
-        <v>5</v>
+      <c r="I492" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.2">
@@ -15003,8 +15010,8 @@
       <c r="H493" s="4">
         <v>42</v>
       </c>
-      <c r="I493" s="4" t="s">
-        <v>5</v>
+      <c r="I493" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.2">
@@ -15032,8 +15039,8 @@
       <c r="H494" s="4">
         <v>33</v>
       </c>
-      <c r="I494" s="4" t="s">
-        <v>5</v>
+      <c r="I494" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="495" spans="1:9" x14ac:dyDescent="0.2">
@@ -15061,8 +15068,8 @@
       <c r="H495" s="4">
         <v>45</v>
       </c>
-      <c r="I495" s="4" t="s">
-        <v>4</v>
+      <c r="I495" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.2">
@@ -15090,8 +15097,8 @@
       <c r="H496" s="4">
         <v>22</v>
       </c>
-      <c r="I496" s="4" t="s">
-        <v>5</v>
+      <c r="I496" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.2">
@@ -15119,8 +15126,8 @@
       <c r="H497" s="4">
         <v>66</v>
       </c>
-      <c r="I497" s="4" t="s">
-        <v>5</v>
+      <c r="I497" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.2">
@@ -15148,8 +15155,8 @@
       <c r="H498" s="4">
         <v>30</v>
       </c>
-      <c r="I498" s="4" t="s">
-        <v>5</v>
+      <c r="I498" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.2">
@@ -15177,8 +15184,8 @@
       <c r="H499" s="4">
         <v>25</v>
       </c>
-      <c r="I499" s="4" t="s">
-        <v>5</v>
+      <c r="I499" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.2">
@@ -15206,8 +15213,8 @@
       <c r="H500" s="4">
         <v>55</v>
       </c>
-      <c r="I500" s="4" t="s">
-        <v>4</v>
+      <c r="I500" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.2">
@@ -15235,8 +15242,8 @@
       <c r="H501" s="4">
         <v>39</v>
       </c>
-      <c r="I501" s="4" t="s">
-        <v>5</v>
+      <c r="I501" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.2">
@@ -15264,8 +15271,8 @@
       <c r="H502" s="4">
         <v>21</v>
       </c>
-      <c r="I502" s="4" t="s">
-        <v>5</v>
+      <c r="I502" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.2">
@@ -15293,8 +15300,8 @@
       <c r="H503" s="4">
         <v>28</v>
       </c>
-      <c r="I503" s="4" t="s">
-        <v>5</v>
+      <c r="I503" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.2">
@@ -15322,8 +15329,8 @@
       <c r="H504" s="4">
         <v>41</v>
       </c>
-      <c r="I504" s="4" t="s">
-        <v>4</v>
+      <c r="I504" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="505" spans="1:9" x14ac:dyDescent="0.2">
@@ -15351,8 +15358,8 @@
       <c r="H505" s="4">
         <v>41</v>
       </c>
-      <c r="I505" s="4" t="s">
-        <v>5</v>
+      <c r="I505" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.2">
@@ -15380,8 +15387,8 @@
       <c r="H506" s="4">
         <v>40</v>
       </c>
-      <c r="I506" s="4" t="s">
-        <v>5</v>
+      <c r="I506" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="507" spans="1:9" x14ac:dyDescent="0.2">
@@ -15409,8 +15416,8 @@
       <c r="H507" s="4">
         <v>38</v>
       </c>
-      <c r="I507" s="4" t="s">
-        <v>5</v>
+      <c r="I507" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.2">
@@ -15438,8 +15445,8 @@
       <c r="H508" s="4">
         <v>35</v>
       </c>
-      <c r="I508" s="4" t="s">
-        <v>4</v>
+      <c r="I508" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.2">
@@ -15467,8 +15474,8 @@
       <c r="H509" s="4">
         <v>21</v>
       </c>
-      <c r="I509" s="4" t="s">
-        <v>5</v>
+      <c r="I509" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.2">
@@ -15496,8 +15503,8 @@
       <c r="H510" s="4">
         <v>21</v>
       </c>
-      <c r="I510" s="4" t="s">
-        <v>5</v>
+      <c r="I510" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.2">
@@ -15525,8 +15532,8 @@
       <c r="H511" s="4">
         <v>64</v>
       </c>
-      <c r="I511" s="4" t="s">
-        <v>5</v>
+      <c r="I511" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.2">
@@ -15554,8 +15561,8 @@
       <c r="H512" s="4">
         <v>46</v>
       </c>
-      <c r="I512" s="4" t="s">
-        <v>4</v>
+      <c r="I512" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="513" spans="1:9" x14ac:dyDescent="0.2">
@@ -15583,8 +15590,8 @@
       <c r="H513" s="4">
         <v>21</v>
       </c>
-      <c r="I513" s="4" t="s">
-        <v>5</v>
+      <c r="I513" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.2">
@@ -15612,8 +15619,8 @@
       <c r="H514" s="4">
         <v>58</v>
       </c>
-      <c r="I514" s="4" t="s">
-        <v>5</v>
+      <c r="I514" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.2">
@@ -15641,8 +15648,8 @@
       <c r="H515" s="4">
         <v>22</v>
       </c>
-      <c r="I515" s="4" t="s">
-        <v>5</v>
+      <c r="I515" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.2">
@@ -15670,8 +15677,8 @@
       <c r="H516" s="4">
         <v>24</v>
       </c>
-      <c r="I516" s="4" t="s">
-        <v>5</v>
+      <c r="I516" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="517" spans="1:9" x14ac:dyDescent="0.2">
@@ -15699,8 +15706,8 @@
       <c r="H517" s="4">
         <v>28</v>
       </c>
-      <c r="I517" s="4" t="s">
-        <v>4</v>
+      <c r="I517" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="518" spans="1:9" x14ac:dyDescent="0.2">
@@ -15728,8 +15735,8 @@
       <c r="H518" s="4">
         <v>53</v>
       </c>
-      <c r="I518" s="4" t="s">
-        <v>4</v>
+      <c r="I518" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.2">
@@ -15757,8 +15764,8 @@
       <c r="H519" s="4">
         <v>51</v>
       </c>
-      <c r="I519" s="4" t="s">
-        <v>5</v>
+      <c r="I519" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.2">
@@ -15786,8 +15793,8 @@
       <c r="H520" s="4">
         <v>41</v>
       </c>
-      <c r="I520" s="4" t="s">
-        <v>5</v>
+      <c r="I520" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="521" spans="1:9" x14ac:dyDescent="0.2">
@@ -15815,8 +15822,8 @@
       <c r="H521" s="4">
         <v>60</v>
       </c>
-      <c r="I521" s="4" t="s">
-        <v>5</v>
+      <c r="I521" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.2">
@@ -15844,8 +15851,8 @@
       <c r="H522" s="4">
         <v>25</v>
       </c>
-      <c r="I522" s="4" t="s">
-        <v>5</v>
+      <c r="I522" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="523" spans="1:9" x14ac:dyDescent="0.2">
@@ -15873,8 +15880,8 @@
       <c r="H523" s="4">
         <v>26</v>
       </c>
-      <c r="I523" s="4" t="s">
-        <v>5</v>
+      <c r="I523" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="524" spans="1:9" x14ac:dyDescent="0.2">
@@ -15902,8 +15909,8 @@
       <c r="H524" s="4">
         <v>26</v>
       </c>
-      <c r="I524" s="4" t="s">
-        <v>5</v>
+      <c r="I524" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.2">
@@ -15931,8 +15938,8 @@
       <c r="H525" s="4">
         <v>45</v>
       </c>
-      <c r="I525" s="4" t="s">
-        <v>4</v>
+      <c r="I525" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="526" spans="1:9" x14ac:dyDescent="0.2">
@@ -15960,8 +15967,8 @@
       <c r="H526" s="4">
         <v>24</v>
       </c>
-      <c r="I526" s="4" t="s">
-        <v>5</v>
+      <c r="I526" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.2">
@@ -15989,8 +15996,8 @@
       <c r="H527" s="4">
         <v>21</v>
       </c>
-      <c r="I527" s="4" t="s">
-        <v>5</v>
+      <c r="I527" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="528" spans="1:9" x14ac:dyDescent="0.2">
@@ -16018,8 +16025,8 @@
       <c r="H528" s="4">
         <v>21</v>
       </c>
-      <c r="I528" s="4" t="s">
-        <v>5</v>
+      <c r="I528" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.2">
@@ -16047,8 +16054,8 @@
       <c r="H529" s="4">
         <v>24</v>
       </c>
-      <c r="I529" s="4" t="s">
-        <v>5</v>
+      <c r="I529" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="530" spans="1:9" x14ac:dyDescent="0.2">
@@ -16076,8 +16083,8 @@
       <c r="H530" s="4">
         <v>22</v>
       </c>
-      <c r="I530" s="4" t="s">
-        <v>5</v>
+      <c r="I530" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.2">
@@ -16105,8 +16112,8 @@
       <c r="H531" s="4">
         <v>31</v>
       </c>
-      <c r="I531" s="4" t="s">
-        <v>5</v>
+      <c r="I531" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.2">
@@ -16134,8 +16141,8 @@
       <c r="H532" s="4">
         <v>22</v>
       </c>
-      <c r="I532" s="4" t="s">
-        <v>5</v>
+      <c r="I532" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="533" spans="1:9" x14ac:dyDescent="0.2">
@@ -16163,8 +16170,8 @@
       <c r="H533" s="4">
         <v>24</v>
       </c>
-      <c r="I533" s="4" t="s">
-        <v>5</v>
+      <c r="I533" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="534" spans="1:9" x14ac:dyDescent="0.2">
@@ -16192,8 +16199,8 @@
       <c r="H534" s="4">
         <v>29</v>
       </c>
-      <c r="I534" s="4" t="s">
-        <v>5</v>
+      <c r="I534" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.2">
@@ -16221,8 +16228,8 @@
       <c r="H535" s="4">
         <v>31</v>
       </c>
-      <c r="I535" s="4" t="s">
-        <v>5</v>
+      <c r="I535" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="536" spans="1:9" x14ac:dyDescent="0.2">
@@ -16250,8 +16257,8 @@
       <c r="H536" s="4">
         <v>24</v>
       </c>
-      <c r="I536" s="4" t="s">
-        <v>5</v>
+      <c r="I536" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.2">
@@ -16279,8 +16286,8 @@
       <c r="H537" s="4">
         <v>23</v>
       </c>
-      <c r="I537" s="4" t="s">
-        <v>4</v>
+      <c r="I537" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.2">
@@ -16308,8 +16315,8 @@
       <c r="H538" s="4">
         <v>46</v>
       </c>
-      <c r="I538" s="4" t="s">
-        <v>5</v>
+      <c r="I538" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.2">
@@ -16337,8 +16344,8 @@
       <c r="H539" s="4">
         <v>67</v>
       </c>
-      <c r="I539" s="4" t="s">
-        <v>5</v>
+      <c r="I539" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.2">
@@ -16366,8 +16373,8 @@
       <c r="H540" s="4">
         <v>23</v>
       </c>
-      <c r="I540" s="4" t="s">
-        <v>5</v>
+      <c r="I540" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.2">
@@ -16395,8 +16402,8 @@
       <c r="H541" s="4">
         <v>32</v>
       </c>
-      <c r="I541" s="4" t="s">
-        <v>4</v>
+      <c r="I541" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="542" spans="1:9" x14ac:dyDescent="0.2">
@@ -16424,8 +16431,8 @@
       <c r="H542" s="4">
         <v>43</v>
       </c>
-      <c r="I542" s="4" t="s">
-        <v>4</v>
+      <c r="I542" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.2">
@@ -16453,8 +16460,8 @@
       <c r="H543" s="4">
         <v>27</v>
       </c>
-      <c r="I543" s="4" t="s">
-        <v>4</v>
+      <c r="I543" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.2">
@@ -16482,8 +16489,8 @@
       <c r="H544" s="4">
         <v>56</v>
       </c>
-      <c r="I544" s="4" t="s">
-        <v>4</v>
+      <c r="I544" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.2">
@@ -16511,8 +16518,8 @@
       <c r="H545" s="4">
         <v>25</v>
       </c>
-      <c r="I545" s="4" t="s">
-        <v>5</v>
+      <c r="I545" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="546" spans="1:9" x14ac:dyDescent="0.2">
@@ -16540,8 +16547,8 @@
       <c r="H546" s="4">
         <v>29</v>
       </c>
-      <c r="I546" s="4" t="s">
-        <v>5</v>
+      <c r="I546" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.2">
@@ -16569,8 +16576,8 @@
       <c r="H547" s="4">
         <v>37</v>
       </c>
-      <c r="I547" s="4" t="s">
-        <v>4</v>
+      <c r="I547" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.2">
@@ -16598,8 +16605,8 @@
       <c r="H548" s="4">
         <v>53</v>
       </c>
-      <c r="I548" s="4" t="s">
-        <v>4</v>
+      <c r="I548" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.2">
@@ -16627,8 +16634,8 @@
       <c r="H549" s="4">
         <v>28</v>
       </c>
-      <c r="I549" s="4" t="s">
-        <v>5</v>
+      <c r="I549" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.2">
@@ -16656,8 +16663,8 @@
       <c r="H550" s="4">
         <v>50</v>
       </c>
-      <c r="I550" s="4" t="s">
-        <v>5</v>
+      <c r="I550" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="551" spans="1:9" x14ac:dyDescent="0.2">
@@ -16685,8 +16692,8 @@
       <c r="H551" s="4">
         <v>37</v>
       </c>
-      <c r="I551" s="4" t="s">
-        <v>5</v>
+      <c r="I551" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="552" spans="1:9" x14ac:dyDescent="0.2">
@@ -16714,8 +16721,8 @@
       <c r="H552" s="4">
         <v>21</v>
       </c>
-      <c r="I552" s="4" t="s">
-        <v>5</v>
+      <c r="I552" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.2">
@@ -16743,8 +16750,8 @@
       <c r="H553" s="4">
         <v>25</v>
       </c>
-      <c r="I553" s="4" t="s">
-        <v>5</v>
+      <c r="I553" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.2">
@@ -16772,8 +16779,8 @@
       <c r="H554" s="4">
         <v>66</v>
       </c>
-      <c r="I554" s="4" t="s">
-        <v>5</v>
+      <c r="I554" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.2">
@@ -16801,8 +16808,8 @@
       <c r="H555" s="4">
         <v>23</v>
       </c>
-      <c r="I555" s="4" t="s">
-        <v>5</v>
+      <c r="I555" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.2">
@@ -16830,8 +16837,8 @@
       <c r="H556" s="4">
         <v>28</v>
       </c>
-      <c r="I556" s="4" t="s">
-        <v>5</v>
+      <c r="I556" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.2">
@@ -16859,8 +16866,8 @@
       <c r="H557" s="4">
         <v>37</v>
       </c>
-      <c r="I557" s="4" t="s">
-        <v>5</v>
+      <c r="I557" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="558" spans="1:9" x14ac:dyDescent="0.2">
@@ -16888,8 +16895,8 @@
       <c r="H558" s="4">
         <v>30</v>
       </c>
-      <c r="I558" s="4" t="s">
-        <v>5</v>
+      <c r="I558" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.2">
@@ -16917,8 +16924,8 @@
       <c r="H559" s="4">
         <v>58</v>
       </c>
-      <c r="I559" s="4" t="s">
-        <v>5</v>
+      <c r="I559" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.2">
@@ -16946,8 +16953,8 @@
       <c r="H560" s="4">
         <v>42</v>
       </c>
-      <c r="I560" s="4" t="s">
-        <v>5</v>
+      <c r="I560" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.2">
@@ -16975,8 +16982,8 @@
       <c r="H561" s="4">
         <v>35</v>
       </c>
-      <c r="I561" s="4" t="s">
-        <v>5</v>
+      <c r="I561" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="562" spans="1:9" x14ac:dyDescent="0.2">
@@ -17004,8 +17011,8 @@
       <c r="H562" s="4">
         <v>54</v>
       </c>
-      <c r="I562" s="4" t="s">
-        <v>4</v>
+      <c r="I562" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.2">
@@ -17033,8 +17040,8 @@
       <c r="H563" s="4">
         <v>28</v>
       </c>
-      <c r="I563" s="4" t="s">
-        <v>4</v>
+      <c r="I563" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.2">
@@ -17062,8 +17069,8 @@
       <c r="H564" s="4">
         <v>24</v>
       </c>
-      <c r="I564" s="4" t="s">
-        <v>5</v>
+      <c r="I564" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.2">
@@ -17091,8 +17098,8 @@
       <c r="H565" s="4">
         <v>32</v>
       </c>
-      <c r="I565" s="4" t="s">
-        <v>5</v>
+      <c r="I565" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.2">
@@ -17120,8 +17127,8 @@
       <c r="H566" s="4">
         <v>27</v>
       </c>
-      <c r="I566" s="4" t="s">
-        <v>5</v>
+      <c r="I566" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.2">
@@ -17149,8 +17156,8 @@
       <c r="H567" s="4">
         <v>22</v>
       </c>
-      <c r="I567" s="4" t="s">
-        <v>5</v>
+      <c r="I567" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.2">
@@ -17178,8 +17185,8 @@
       <c r="H568" s="4">
         <v>21</v>
       </c>
-      <c r="I568" s="4" t="s">
-        <v>5</v>
+      <c r="I568" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.2">
@@ -17207,8 +17214,8 @@
       <c r="H569" s="4">
         <v>46</v>
       </c>
-      <c r="I569" s="4" t="s">
-        <v>5</v>
+      <c r="I569" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.2">
@@ -17236,8 +17243,8 @@
       <c r="H570" s="4">
         <v>37</v>
       </c>
-      <c r="I570" s="4" t="s">
-        <v>5</v>
+      <c r="I570" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.2">
@@ -17265,8 +17272,8 @@
       <c r="H571" s="4">
         <v>33</v>
       </c>
-      <c r="I571" s="4" t="s">
-        <v>4</v>
+      <c r="I571" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.2">
@@ -17294,8 +17301,8 @@
       <c r="H572" s="4">
         <v>39</v>
       </c>
-      <c r="I572" s="4" t="s">
-        <v>5</v>
+      <c r="I572" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.2">
@@ -17323,8 +17330,8 @@
       <c r="H573" s="4">
         <v>21</v>
       </c>
-      <c r="I573" s="4" t="s">
-        <v>5</v>
+      <c r="I573" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.2">
@@ -17352,8 +17359,8 @@
       <c r="H574" s="4">
         <v>22</v>
       </c>
-      <c r="I574" s="4" t="s">
-        <v>5</v>
+      <c r="I574" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.2">
@@ -17381,8 +17388,8 @@
       <c r="H575" s="4">
         <v>22</v>
       </c>
-      <c r="I575" s="4" t="s">
-        <v>5</v>
+      <c r="I575" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="576" spans="1:9" x14ac:dyDescent="0.2">
@@ -17410,8 +17417,8 @@
       <c r="H576" s="4">
         <v>23</v>
       </c>
-      <c r="I576" s="4" t="s">
-        <v>5</v>
+      <c r="I576" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.2">
@@ -17439,8 +17446,8 @@
       <c r="H577" s="4">
         <v>25</v>
       </c>
-      <c r="I577" s="4" t="s">
-        <v>5</v>
+      <c r="I577" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.2">
@@ -17468,8 +17475,8 @@
       <c r="H578" s="4">
         <v>35</v>
       </c>
-      <c r="I578" s="4" t="s">
-        <v>5</v>
+      <c r="I578" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.2">
@@ -17497,8 +17504,8 @@
       <c r="H579" s="4">
         <v>21</v>
       </c>
-      <c r="I579" s="4" t="s">
-        <v>4</v>
+      <c r="I579" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.2">
@@ -17526,8 +17533,8 @@
       <c r="H580" s="4">
         <v>36</v>
       </c>
-      <c r="I580" s="4" t="s">
-        <v>5</v>
+      <c r="I580" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.2">
@@ -17555,8 +17562,8 @@
       <c r="H581" s="4">
         <v>62</v>
       </c>
-      <c r="I581" s="4" t="s">
-        <v>4</v>
+      <c r="I581" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.2">
@@ -17584,8 +17591,8 @@
       <c r="H582" s="4">
         <v>21</v>
       </c>
-      <c r="I582" s="4" t="s">
-        <v>4</v>
+      <c r="I582" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.2">
@@ -17613,8 +17620,8 @@
       <c r="H583" s="4">
         <v>27</v>
       </c>
-      <c r="I583" s="4" t="s">
-        <v>5</v>
+      <c r="I583" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.2">
@@ -17642,8 +17649,8 @@
       <c r="H584" s="4">
         <v>62</v>
       </c>
-      <c r="I584" s="4" t="s">
-        <v>5</v>
+      <c r="I584" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.2">
@@ -17671,8 +17678,8 @@
       <c r="H585" s="4">
         <v>42</v>
       </c>
-      <c r="I585" s="4" t="s">
-        <v>5</v>
+      <c r="I585" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.2">
@@ -17700,8 +17707,8 @@
       <c r="H586" s="4">
         <v>52</v>
       </c>
-      <c r="I586" s="4" t="s">
-        <v>4</v>
+      <c r="I586" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.2">
@@ -17729,8 +17736,8 @@
       <c r="H587" s="4">
         <v>22</v>
       </c>
-      <c r="I587" s="4" t="s">
-        <v>5</v>
+      <c r="I587" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.2">
@@ -17758,8 +17765,8 @@
       <c r="H588" s="4">
         <v>41</v>
       </c>
-      <c r="I588" s="4" t="s">
-        <v>4</v>
+      <c r="I588" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.2">
@@ -17787,8 +17794,8 @@
       <c r="H589" s="4">
         <v>29</v>
       </c>
-      <c r="I589" s="4" t="s">
-        <v>5</v>
+      <c r="I589" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="590" spans="1:9" x14ac:dyDescent="0.2">
@@ -17816,8 +17823,8 @@
       <c r="H590" s="4">
         <v>52</v>
       </c>
-      <c r="I590" s="4" t="s">
-        <v>4</v>
+      <c r="I590" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.2">
@@ -17845,8 +17852,8 @@
       <c r="H591" s="4">
         <v>25</v>
       </c>
-      <c r="I591" s="4" t="s">
-        <v>5</v>
+      <c r="I591" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.2">
@@ -17874,8 +17881,8 @@
       <c r="H592" s="4">
         <v>45</v>
       </c>
-      <c r="I592" s="4" t="s">
-        <v>4</v>
+      <c r="I592" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="593" spans="1:9" x14ac:dyDescent="0.2">
@@ -17903,8 +17910,8 @@
       <c r="H593" s="4">
         <v>24</v>
       </c>
-      <c r="I593" s="4" t="s">
-        <v>5</v>
+      <c r="I593" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.2">
@@ -17932,8 +17939,8 @@
       <c r="H594" s="4">
         <v>44</v>
       </c>
-      <c r="I594" s="4" t="s">
-        <v>4</v>
+      <c r="I594" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.2">
@@ -17961,8 +17968,8 @@
       <c r="H595" s="4">
         <v>25</v>
       </c>
-      <c r="I595" s="4" t="s">
-        <v>5</v>
+      <c r="I595" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.2">
@@ -17990,8 +17997,8 @@
       <c r="H596" s="4">
         <v>34</v>
       </c>
-      <c r="I596" s="4" t="s">
-        <v>5</v>
+      <c r="I596" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.2">
@@ -18019,8 +18026,8 @@
       <c r="H597" s="4">
         <v>22</v>
       </c>
-      <c r="I597" s="4" t="s">
-        <v>4</v>
+      <c r="I597" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="598" spans="1:9" x14ac:dyDescent="0.2">
@@ -18048,8 +18055,8 @@
       <c r="H598" s="4">
         <v>46</v>
       </c>
-      <c r="I598" s="4" t="s">
-        <v>5</v>
+      <c r="I598" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.2">
@@ -18077,8 +18084,8 @@
       <c r="H599" s="4">
         <v>21</v>
       </c>
-      <c r="I599" s="4" t="s">
-        <v>5</v>
+      <c r="I599" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="600" spans="1:9" x14ac:dyDescent="0.2">
@@ -18106,8 +18113,8 @@
       <c r="H600" s="4">
         <v>38</v>
       </c>
-      <c r="I600" s="4" t="s">
-        <v>4</v>
+      <c r="I600" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.2">
@@ -18135,8 +18142,8 @@
       <c r="H601" s="4">
         <v>26</v>
       </c>
-      <c r="I601" s="4" t="s">
-        <v>5</v>
+      <c r="I601" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="602" spans="1:9" x14ac:dyDescent="0.2">
@@ -18164,8 +18171,8 @@
       <c r="H602" s="4">
         <v>24</v>
       </c>
-      <c r="I602" s="4" t="s">
-        <v>5</v>
+      <c r="I602" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.2">
@@ -18193,8 +18200,8 @@
       <c r="H603" s="4">
         <v>28</v>
       </c>
-      <c r="I603" s="4" t="s">
-        <v>5</v>
+      <c r="I603" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.2">
@@ -18222,8 +18229,8 @@
       <c r="H604" s="4">
         <v>30</v>
       </c>
-      <c r="I604" s="4" t="s">
-        <v>5</v>
+      <c r="I604" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.2">
@@ -18251,8 +18258,8 @@
       <c r="H605" s="4">
         <v>54</v>
       </c>
-      <c r="I605" s="4" t="s">
-        <v>4</v>
+      <c r="I605" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.2">
@@ -18280,8 +18287,8 @@
       <c r="H606" s="4">
         <v>36</v>
       </c>
-      <c r="I606" s="4" t="s">
-        <v>4</v>
+      <c r="I606" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.2">
@@ -18309,8 +18316,8 @@
       <c r="H607" s="4">
         <v>21</v>
       </c>
-      <c r="I607" s="4" t="s">
-        <v>5</v>
+      <c r="I607" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.2">
@@ -18338,8 +18345,8 @@
       <c r="H608" s="4">
         <v>22</v>
       </c>
-      <c r="I608" s="4" t="s">
-        <v>4</v>
+      <c r="I608" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.2">
@@ -18367,8 +18374,8 @@
       <c r="H609" s="4">
         <v>25</v>
       </c>
-      <c r="I609" s="4" t="s">
-        <v>5</v>
+      <c r="I609" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="610" spans="1:9" x14ac:dyDescent="0.2">
@@ -18396,8 +18403,8 @@
       <c r="H610" s="4">
         <v>27</v>
       </c>
-      <c r="I610" s="4" t="s">
-        <v>5</v>
+      <c r="I610" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.2">
@@ -18425,8 +18432,8 @@
       <c r="H611" s="4">
         <v>23</v>
       </c>
-      <c r="I611" s="4" t="s">
-        <v>5</v>
+      <c r="I611" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.2">
@@ -18454,8 +18461,8 @@
       <c r="H612" s="4">
         <v>24</v>
       </c>
-      <c r="I612" s="4" t="s">
-        <v>5</v>
+      <c r="I612" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.2">
@@ -18483,8 +18490,8 @@
       <c r="H613" s="4">
         <v>36</v>
       </c>
-      <c r="I613" s="4" t="s">
-        <v>4</v>
+      <c r="I613" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.2">
@@ -18512,8 +18519,8 @@
       <c r="H614" s="4">
         <v>40</v>
       </c>
-      <c r="I614" s="4" t="s">
-        <v>4</v>
+      <c r="I614" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.2">
@@ -18541,8 +18548,8 @@
       <c r="H615" s="4">
         <v>26</v>
       </c>
-      <c r="I615" s="4" t="s">
-        <v>5</v>
+      <c r="I615" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="616" spans="1:9" x14ac:dyDescent="0.2">
@@ -18570,8 +18577,8 @@
       <c r="H616" s="4">
         <v>50</v>
       </c>
-      <c r="I616" s="4" t="s">
-        <v>4</v>
+      <c r="I616" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.2">
@@ -18599,8 +18606,8 @@
       <c r="H617" s="4">
         <v>27</v>
       </c>
-      <c r="I617" s="4" t="s">
-        <v>5</v>
+      <c r="I617" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="618" spans="1:9" x14ac:dyDescent="0.2">
@@ -18628,8 +18635,8 @@
       <c r="H618" s="4">
         <v>30</v>
       </c>
-      <c r="I618" s="4" t="s">
-        <v>5</v>
+      <c r="I618" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.2">
@@ -18657,8 +18664,8 @@
       <c r="H619" s="4">
         <v>23</v>
       </c>
-      <c r="I619" s="4" t="s">
-        <v>5</v>
+      <c r="I619" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.2">
@@ -18686,8 +18693,8 @@
       <c r="H620" s="4">
         <v>50</v>
       </c>
-      <c r="I620" s="4" t="s">
-        <v>4</v>
+      <c r="I620" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.2">
@@ -18715,8 +18722,8 @@
       <c r="H621" s="4">
         <v>24</v>
       </c>
-      <c r="I621" s="4" t="s">
-        <v>4</v>
+      <c r="I621" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.2">
@@ -18744,8 +18751,8 @@
       <c r="H622" s="4">
         <v>28</v>
       </c>
-      <c r="I622" s="4" t="s">
-        <v>5</v>
+      <c r="I622" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.2">
@@ -18773,8 +18780,8 @@
       <c r="H623" s="4">
         <v>28</v>
       </c>
-      <c r="I623" s="4" t="s">
-        <v>5</v>
+      <c r="I623" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.2">
@@ -18802,8 +18809,8 @@
       <c r="H624" s="4">
         <v>45</v>
       </c>
-      <c r="I624" s="4" t="s">
-        <v>5</v>
+      <c r="I624" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="625" spans="1:9" x14ac:dyDescent="0.2">
@@ -18831,8 +18838,8 @@
       <c r="H625" s="4">
         <v>21</v>
       </c>
-      <c r="I625" s="4" t="s">
-        <v>5</v>
+      <c r="I625" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="626" spans="1:9" x14ac:dyDescent="0.2">
@@ -18860,8 +18867,8 @@
       <c r="H626" s="4">
         <v>21</v>
       </c>
-      <c r="I626" s="4" t="s">
-        <v>5</v>
+      <c r="I626" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.2">
@@ -18889,8 +18896,8 @@
       <c r="H627" s="4">
         <v>29</v>
       </c>
-      <c r="I627" s="4" t="s">
-        <v>5</v>
+      <c r="I627" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.2">
@@ -18918,8 +18925,8 @@
       <c r="H628" s="4">
         <v>21</v>
       </c>
-      <c r="I628" s="4" t="s">
-        <v>5</v>
+      <c r="I628" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.2">
@@ -18947,8 +18954,8 @@
       <c r="H629" s="4">
         <v>21</v>
       </c>
-      <c r="I629" s="4" t="s">
-        <v>5</v>
+      <c r="I629" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="630" spans="1:9" x14ac:dyDescent="0.2">
@@ -18976,8 +18983,8 @@
       <c r="H630" s="4">
         <v>45</v>
       </c>
-      <c r="I630" s="4" t="s">
-        <v>5</v>
+      <c r="I630" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.2">
@@ -19005,8 +19012,8 @@
       <c r="H631" s="4">
         <v>21</v>
       </c>
-      <c r="I631" s="4" t="s">
-        <v>5</v>
+      <c r="I631" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.2">
@@ -19034,8 +19041,8 @@
       <c r="H632" s="4">
         <v>34</v>
       </c>
-      <c r="I632" s="4" t="s">
-        <v>4</v>
+      <c r="I632" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.2">
@@ -19063,8 +19070,8 @@
       <c r="H633" s="4">
         <v>24</v>
       </c>
-      <c r="I633" s="4" t="s">
-        <v>5</v>
+      <c r="I633" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.2">
@@ -19092,8 +19099,8 @@
       <c r="H634" s="4">
         <v>23</v>
       </c>
-      <c r="I634" s="4" t="s">
-        <v>5</v>
+      <c r="I634" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.2">
@@ -19121,8 +19128,8 @@
       <c r="H635" s="4">
         <v>22</v>
       </c>
-      <c r="I635" s="4" t="s">
-        <v>5</v>
+      <c r="I635" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.2">
@@ -19150,8 +19157,8 @@
       <c r="H636" s="4">
         <v>31</v>
       </c>
-      <c r="I636" s="4" t="s">
-        <v>5</v>
+      <c r="I636" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.2">
@@ -19179,8 +19186,8 @@
       <c r="H637" s="4">
         <v>38</v>
       </c>
-      <c r="I637" s="4" t="s">
-        <v>4</v>
+      <c r="I637" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="638" spans="1:9" x14ac:dyDescent="0.2">
@@ -19208,8 +19215,8 @@
       <c r="H638" s="4">
         <v>48</v>
       </c>
-      <c r="I638" s="4" t="s">
-        <v>5</v>
+      <c r="I638" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.2">
@@ -19237,8 +19244,8 @@
       <c r="H639" s="4">
         <v>23</v>
       </c>
-      <c r="I639" s="4" t="s">
-        <v>5</v>
+      <c r="I639" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.2">
@@ -19266,8 +19273,8 @@
       <c r="H640" s="4">
         <v>32</v>
       </c>
-      <c r="I640" s="4" t="s">
-        <v>4</v>
+      <c r="I640" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.2">
@@ -19295,8 +19302,8 @@
       <c r="H641" s="4">
         <v>28</v>
       </c>
-      <c r="I641" s="4" t="s">
-        <v>5</v>
+      <c r="I641" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="642" spans="1:9" x14ac:dyDescent="0.2">
@@ -19324,8 +19331,8 @@
       <c r="H642" s="4">
         <v>27</v>
       </c>
-      <c r="I642" s="4" t="s">
-        <v>5</v>
+      <c r="I642" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="643" spans="1:9" x14ac:dyDescent="0.2">
@@ -19353,8 +19360,8 @@
       <c r="H643" s="4">
         <v>24</v>
       </c>
-      <c r="I643" s="4" t="s">
-        <v>5</v>
+      <c r="I643" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.2">
@@ -19382,8 +19389,8 @@
       <c r="H644" s="4">
         <v>50</v>
       </c>
-      <c r="I644" s="4" t="s">
-        <v>4</v>
+      <c r="I644" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="645" spans="1:9" x14ac:dyDescent="0.2">
@@ -19411,8 +19418,8 @@
       <c r="H645" s="4">
         <v>31</v>
       </c>
-      <c r="I645" s="4" t="s">
-        <v>5</v>
+      <c r="I645" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.2">
@@ -19440,8 +19447,8 @@
       <c r="H646" s="4">
         <v>27</v>
       </c>
-      <c r="I646" s="4" t="s">
-        <v>5</v>
+      <c r="I646" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="647" spans="1:9" x14ac:dyDescent="0.2">
@@ -19469,8 +19476,8 @@
       <c r="H647" s="4">
         <v>30</v>
       </c>
-      <c r="I647" s="4" t="s">
-        <v>5</v>
+      <c r="I647" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.2">
@@ -19498,8 +19505,8 @@
       <c r="H648" s="4">
         <v>33</v>
       </c>
-      <c r="I648" s="4" t="s">
-        <v>4</v>
+      <c r="I648" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.2">
@@ -19527,8 +19534,8 @@
       <c r="H649" s="4">
         <v>22</v>
       </c>
-      <c r="I649" s="4" t="s">
-        <v>4</v>
+      <c r="I649" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.2">
@@ -19556,8 +19563,8 @@
       <c r="H650" s="4">
         <v>42</v>
       </c>
-      <c r="I650" s="4" t="s">
-        <v>4</v>
+      <c r="I650" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="651" spans="1:9" x14ac:dyDescent="0.2">
@@ -19585,8 +19592,8 @@
       <c r="H651" s="4">
         <v>23</v>
       </c>
-      <c r="I651" s="4" t="s">
-        <v>5</v>
+      <c r="I651" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.2">
@@ -19614,8 +19621,8 @@
       <c r="H652" s="4">
         <v>23</v>
       </c>
-      <c r="I652" s="4" t="s">
-        <v>5</v>
+      <c r="I652" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="653" spans="1:9" x14ac:dyDescent="0.2">
@@ -19643,8 +19650,8 @@
       <c r="H653" s="4">
         <v>27</v>
       </c>
-      <c r="I653" s="4" t="s">
-        <v>5</v>
+      <c r="I653" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="654" spans="1:9" x14ac:dyDescent="0.2">
@@ -19672,8 +19679,8 @@
       <c r="H654" s="4">
         <v>28</v>
       </c>
-      <c r="I654" s="4" t="s">
-        <v>5</v>
+      <c r="I654" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="655" spans="1:9" x14ac:dyDescent="0.2">
@@ -19701,8 +19708,8 @@
       <c r="H655" s="4">
         <v>27</v>
       </c>
-      <c r="I655" s="4" t="s">
-        <v>5</v>
+      <c r="I655" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="656" spans="1:9" x14ac:dyDescent="0.2">
@@ -19730,8 +19737,8 @@
       <c r="H656" s="4">
         <v>22</v>
       </c>
-      <c r="I656" s="4" t="s">
-        <v>5</v>
+      <c r="I656" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="657" spans="1:9" x14ac:dyDescent="0.2">
@@ -19759,8 +19766,8 @@
       <c r="H657" s="4">
         <v>25</v>
       </c>
-      <c r="I657" s="4" t="s">
-        <v>4</v>
+      <c r="I657" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="658" spans="1:9" x14ac:dyDescent="0.2">
@@ -19788,8 +19795,8 @@
       <c r="H658" s="4">
         <v>22</v>
       </c>
-      <c r="I658" s="4" t="s">
-        <v>5</v>
+      <c r="I658" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.2">
@@ -19817,8 +19824,8 @@
       <c r="H659" s="4">
         <v>41</v>
       </c>
-      <c r="I659" s="4" t="s">
-        <v>5</v>
+      <c r="I659" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.2">
@@ -19846,8 +19853,8 @@
       <c r="H660" s="4">
         <v>51</v>
       </c>
-      <c r="I660" s="4" t="s">
-        <v>5</v>
+      <c r="I660" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="661" spans="1:9" x14ac:dyDescent="0.2">
@@ -19875,8 +19882,8 @@
       <c r="H661" s="4">
         <v>27</v>
       </c>
-      <c r="I661" s="4" t="s">
-        <v>4</v>
+      <c r="I661" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.2">
@@ -19904,8 +19911,8 @@
       <c r="H662" s="4">
         <v>54</v>
       </c>
-      <c r="I662" s="4" t="s">
-        <v>5</v>
+      <c r="I662" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="663" spans="1:9" x14ac:dyDescent="0.2">
@@ -19933,8 +19940,8 @@
       <c r="H663" s="4">
         <v>22</v>
       </c>
-      <c r="I663" s="4" t="s">
-        <v>4</v>
+      <c r="I663" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="664" spans="1:9" x14ac:dyDescent="0.2">
@@ -19962,8 +19969,8 @@
       <c r="H664" s="4">
         <v>43</v>
       </c>
-      <c r="I664" s="4" t="s">
-        <v>4</v>
+      <c r="I664" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="665" spans="1:9" x14ac:dyDescent="0.2">
@@ -19991,8 +19998,8 @@
       <c r="H665" s="4">
         <v>40</v>
       </c>
-      <c r="I665" s="4" t="s">
-        <v>4</v>
+      <c r="I665" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="666" spans="1:9" x14ac:dyDescent="0.2">
@@ -20020,8 +20027,8 @@
       <c r="H666" s="4">
         <v>40</v>
       </c>
-      <c r="I666" s="4" t="s">
-        <v>4</v>
+      <c r="I666" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="667" spans="1:9" x14ac:dyDescent="0.2">
@@ -20049,8 +20056,8 @@
       <c r="H667" s="4">
         <v>24</v>
       </c>
-      <c r="I667" s="4" t="s">
-        <v>5</v>
+      <c r="I667" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.2">
@@ -20078,8 +20085,8 @@
       <c r="H668" s="4">
         <v>70</v>
       </c>
-      <c r="I668" s="4" t="s">
-        <v>4</v>
+      <c r="I668" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.2">
@@ -20107,8 +20114,8 @@
       <c r="H669" s="4">
         <v>40</v>
       </c>
-      <c r="I669" s="4" t="s">
-        <v>4</v>
+      <c r="I669" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.2">
@@ -20136,8 +20143,8 @@
       <c r="H670" s="4">
         <v>43</v>
       </c>
-      <c r="I670" s="4" t="s">
-        <v>5</v>
+      <c r="I670" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="671" spans="1:9" x14ac:dyDescent="0.2">
@@ -20165,8 +20172,8 @@
       <c r="H671" s="4">
         <v>45</v>
       </c>
-      <c r="I671" s="4" t="s">
-        <v>5</v>
+      <c r="I671" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.2">
@@ -20194,8 +20201,8 @@
       <c r="H672" s="4">
         <v>49</v>
       </c>
-      <c r="I672" s="4" t="s">
-        <v>5</v>
+      <c r="I672" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="673" spans="1:9" x14ac:dyDescent="0.2">
@@ -20223,8 +20230,8 @@
       <c r="H673" s="4">
         <v>21</v>
       </c>
-      <c r="I673" s="4" t="s">
-        <v>5</v>
+      <c r="I673" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="674" spans="1:9" x14ac:dyDescent="0.2">
@@ -20252,8 +20259,8 @@
       <c r="H674" s="4">
         <v>47</v>
       </c>
-      <c r="I674" s="4" t="s">
-        <v>5</v>
+      <c r="I674" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="675" spans="1:9" x14ac:dyDescent="0.2">
@@ -20281,8 +20288,8 @@
       <c r="H675" s="4">
         <v>22</v>
       </c>
-      <c r="I675" s="4" t="s">
-        <v>5</v>
+      <c r="I675" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.2">
@@ -20310,8 +20317,8 @@
       <c r="H676" s="4">
         <v>68</v>
       </c>
-      <c r="I676" s="4" t="s">
-        <v>5</v>
+      <c r="I676" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="677" spans="1:9" x14ac:dyDescent="0.2">
@@ -20339,8 +20346,8 @@
       <c r="H677" s="4">
         <v>31</v>
       </c>
-      <c r="I677" s="4" t="s">
-        <v>4</v>
+      <c r="I677" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="678" spans="1:9" x14ac:dyDescent="0.2">
@@ -20368,8 +20375,8 @@
       <c r="H678" s="4">
         <v>53</v>
       </c>
-      <c r="I678" s="4" t="s">
-        <v>4</v>
+      <c r="I678" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="679" spans="1:9" x14ac:dyDescent="0.2">
@@ -20397,8 +20404,8 @@
       <c r="H679" s="4">
         <v>25</v>
       </c>
-      <c r="I679" s="4" t="s">
-        <v>5</v>
+      <c r="I679" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="680" spans="1:9" x14ac:dyDescent="0.2">
@@ -20426,8 +20433,8 @@
       <c r="H680" s="4">
         <v>25</v>
       </c>
-      <c r="I680" s="4" t="s">
-        <v>4</v>
+      <c r="I680" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="681" spans="1:9" x14ac:dyDescent="0.2">
@@ -20455,8 +20462,8 @@
       <c r="H681" s="4">
         <v>23</v>
       </c>
-      <c r="I681" s="4" t="s">
-        <v>5</v>
+      <c r="I681" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="682" spans="1:9" x14ac:dyDescent="0.2">
@@ -20484,8 +20491,8 @@
       <c r="H682" s="4">
         <v>22</v>
       </c>
-      <c r="I682" s="4" t="s">
-        <v>5</v>
+      <c r="I682" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="683" spans="1:9" x14ac:dyDescent="0.2">
@@ -20513,8 +20520,8 @@
       <c r="H683" s="4">
         <v>26</v>
       </c>
-      <c r="I683" s="4" t="s">
-        <v>4</v>
+      <c r="I683" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="684" spans="1:9" x14ac:dyDescent="0.2">
@@ -20542,8 +20549,8 @@
       <c r="H684" s="4">
         <v>22</v>
       </c>
-      <c r="I684" s="4" t="s">
-        <v>5</v>
+      <c r="I684" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="685" spans="1:9" x14ac:dyDescent="0.2">
@@ -20571,8 +20578,8 @@
       <c r="H685" s="4">
         <v>27</v>
       </c>
-      <c r="I685" s="4" t="s">
-        <v>4</v>
+      <c r="I685" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="686" spans="1:9" x14ac:dyDescent="0.2">
@@ -20600,8 +20607,8 @@
       <c r="H686" s="4">
         <v>69</v>
       </c>
-      <c r="I686" s="4" t="s">
-        <v>5</v>
+      <c r="I686" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="687" spans="1:9" x14ac:dyDescent="0.2">
@@ -20629,8 +20636,8 @@
       <c r="H687" s="4">
         <v>25</v>
       </c>
-      <c r="I687" s="4" t="s">
-        <v>5</v>
+      <c r="I687" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.2">
@@ -20658,8 +20665,8 @@
       <c r="H688" s="4">
         <v>22</v>
       </c>
-      <c r="I688" s="4" t="s">
-        <v>5</v>
+      <c r="I688" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="689" spans="1:9" x14ac:dyDescent="0.2">
@@ -20687,8 +20694,8 @@
       <c r="H689" s="4">
         <v>29</v>
       </c>
-      <c r="I689" s="4" t="s">
-        <v>5</v>
+      <c r="I689" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="690" spans="1:9" x14ac:dyDescent="0.2">
@@ -20716,8 +20723,8 @@
       <c r="H690" s="4">
         <v>23</v>
       </c>
-      <c r="I690" s="4" t="s">
-        <v>5</v>
+      <c r="I690" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.2">
@@ -20745,8 +20752,8 @@
       <c r="H691" s="4">
         <v>46</v>
       </c>
-      <c r="I691" s="4" t="s">
-        <v>4</v>
+      <c r="I691" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.2">
@@ -20774,8 +20781,8 @@
       <c r="H692" s="4">
         <v>34</v>
       </c>
-      <c r="I692" s="4" t="s">
-        <v>5</v>
+      <c r="I692" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="693" spans="1:9" x14ac:dyDescent="0.2">
@@ -20803,8 +20810,8 @@
       <c r="H693" s="4">
         <v>44</v>
       </c>
-      <c r="I693" s="4" t="s">
-        <v>4</v>
+      <c r="I693" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.2">
@@ -20832,8 +20839,8 @@
       <c r="H694" s="4">
         <v>23</v>
       </c>
-      <c r="I694" s="4" t="s">
-        <v>5</v>
+      <c r="I694" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.2">
@@ -20861,8 +20868,8 @@
       <c r="H695" s="4">
         <v>43</v>
       </c>
-      <c r="I695" s="4" t="s">
-        <v>4</v>
+      <c r="I695" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="696" spans="1:9" x14ac:dyDescent="0.2">
@@ -20890,8 +20897,8 @@
       <c r="H696" s="4">
         <v>25</v>
       </c>
-      <c r="I696" s="4" t="s">
-        <v>5</v>
+      <c r="I696" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="697" spans="1:9" x14ac:dyDescent="0.2">
@@ -20919,8 +20926,8 @@
       <c r="H697" s="4">
         <v>43</v>
       </c>
-      <c r="I697" s="4" t="s">
-        <v>4</v>
+      <c r="I697" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="698" spans="1:9" x14ac:dyDescent="0.2">
@@ -20948,8 +20955,8 @@
       <c r="H698" s="4">
         <v>31</v>
       </c>
-      <c r="I698" s="4" t="s">
-        <v>4</v>
+      <c r="I698" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="699" spans="1:9" x14ac:dyDescent="0.2">
@@ -20977,8 +20984,8 @@
       <c r="H699" s="4">
         <v>22</v>
       </c>
-      <c r="I699" s="4" t="s">
-        <v>5</v>
+      <c r="I699" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="700" spans="1:9" x14ac:dyDescent="0.2">
@@ -21006,8 +21013,8 @@
       <c r="H700" s="4">
         <v>28</v>
       </c>
-      <c r="I700" s="4" t="s">
-        <v>5</v>
+      <c r="I700" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="701" spans="1:9" x14ac:dyDescent="0.2">
@@ -21035,8 +21042,8 @@
       <c r="H701" s="4">
         <v>26</v>
       </c>
-      <c r="I701" s="4" t="s">
-        <v>5</v>
+      <c r="I701" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="702" spans="1:9" x14ac:dyDescent="0.2">
@@ -21064,8 +21071,8 @@
       <c r="H702" s="4">
         <v>26</v>
       </c>
-      <c r="I702" s="4" t="s">
-        <v>5</v>
+      <c r="I702" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="703" spans="1:9" x14ac:dyDescent="0.2">
@@ -21093,8 +21100,8 @@
       <c r="H703" s="4">
         <v>49</v>
       </c>
-      <c r="I703" s="4" t="s">
-        <v>4</v>
+      <c r="I703" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="704" spans="1:9" x14ac:dyDescent="0.2">
@@ -21122,8 +21129,8 @@
       <c r="H704" s="4">
         <v>52</v>
       </c>
-      <c r="I704" s="4" t="s">
-        <v>4</v>
+      <c r="I704" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="705" spans="1:9" x14ac:dyDescent="0.2">
@@ -21151,8 +21158,8 @@
       <c r="H705" s="4">
         <v>41</v>
       </c>
-      <c r="I705" s="4" t="s">
-        <v>5</v>
+      <c r="I705" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.2">
@@ -21180,8 +21187,8 @@
       <c r="H706" s="4">
         <v>27</v>
       </c>
-      <c r="I706" s="4" t="s">
-        <v>5</v>
+      <c r="I706" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="707" spans="1:9" x14ac:dyDescent="0.2">
@@ -21209,8 +21216,8 @@
       <c r="H707" s="4">
         <v>28</v>
       </c>
-      <c r="I707" s="4" t="s">
-        <v>5</v>
+      <c r="I707" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.2">
@@ -21238,8 +21245,8 @@
       <c r="H708" s="4">
         <v>30</v>
       </c>
-      <c r="I708" s="4" t="s">
-        <v>4</v>
+      <c r="I708" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="709" spans="1:9" x14ac:dyDescent="0.2">
@@ -21267,8 +21274,8 @@
       <c r="H709" s="4">
         <v>22</v>
       </c>
-      <c r="I709" s="4" t="s">
-        <v>5</v>
+      <c r="I709" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="710" spans="1:9" x14ac:dyDescent="0.2">
@@ -21296,8 +21303,8 @@
       <c r="H710" s="4">
         <v>45</v>
       </c>
-      <c r="I710" s="4" t="s">
-        <v>4</v>
+      <c r="I710" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="711" spans="1:9" x14ac:dyDescent="0.2">
@@ -21325,8 +21332,8 @@
       <c r="H711" s="4">
         <v>23</v>
       </c>
-      <c r="I711" s="4" t="s">
-        <v>4</v>
+      <c r="I711" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="712" spans="1:9" x14ac:dyDescent="0.2">
@@ -21354,8 +21361,8 @@
       <c r="H712" s="4">
         <v>24</v>
       </c>
-      <c r="I712" s="4" t="s">
-        <v>5</v>
+      <c r="I712" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="713" spans="1:9" x14ac:dyDescent="0.2">
@@ -21383,8 +21390,8 @@
       <c r="H713" s="4">
         <v>40</v>
       </c>
-      <c r="I713" s="4" t="s">
-        <v>5</v>
+      <c r="I713" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="714" spans="1:9" x14ac:dyDescent="0.2">
@@ -21412,8 +21419,8 @@
       <c r="H714" s="4">
         <v>38</v>
       </c>
-      <c r="I714" s="4" t="s">
-        <v>4</v>
+      <c r="I714" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="715" spans="1:9" x14ac:dyDescent="0.2">
@@ -21441,8 +21448,8 @@
       <c r="H715" s="4">
         <v>21</v>
       </c>
-      <c r="I715" s="4" t="s">
-        <v>5</v>
+      <c r="I715" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.2">
@@ -21470,8 +21477,8 @@
       <c r="H716" s="4">
         <v>32</v>
       </c>
-      <c r="I716" s="4" t="s">
-        <v>5</v>
+      <c r="I716" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="717" spans="1:9" x14ac:dyDescent="0.2">
@@ -21499,8 +21506,8 @@
       <c r="H717" s="4">
         <v>34</v>
       </c>
-      <c r="I717" s="4" t="s">
-        <v>4</v>
+      <c r="I717" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="718" spans="1:9" x14ac:dyDescent="0.2">
@@ -21528,8 +21535,8 @@
       <c r="H718" s="4">
         <v>31</v>
       </c>
-      <c r="I718" s="4" t="s">
-        <v>4</v>
+      <c r="I718" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="719" spans="1:9" x14ac:dyDescent="0.2">
@@ -21557,8 +21564,8 @@
       <c r="H719" s="4">
         <v>56</v>
       </c>
-      <c r="I719" s="4" t="s">
-        <v>5</v>
+      <c r="I719" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="720" spans="1:9" x14ac:dyDescent="0.2">
@@ -21586,8 +21593,8 @@
       <c r="H720" s="4">
         <v>24</v>
       </c>
-      <c r="I720" s="4" t="s">
-        <v>5</v>
+      <c r="I720" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="721" spans="1:9" x14ac:dyDescent="0.2">
@@ -21615,8 +21622,8 @@
       <c r="H721" s="4">
         <v>52</v>
       </c>
-      <c r="I721" s="4" t="s">
-        <v>4</v>
+      <c r="I721" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="722" spans="1:9" x14ac:dyDescent="0.2">
@@ -21644,8 +21651,8 @@
       <c r="H722" s="4">
         <v>34</v>
       </c>
-      <c r="I722" s="4" t="s">
-        <v>5</v>
+      <c r="I722" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="723" spans="1:9" x14ac:dyDescent="0.2">
@@ -21673,8 +21680,8 @@
       <c r="H723" s="4">
         <v>21</v>
       </c>
-      <c r="I723" s="4" t="s">
-        <v>5</v>
+      <c r="I723" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.2">
@@ -21702,8 +21709,8 @@
       <c r="H724" s="4">
         <v>42</v>
       </c>
-      <c r="I724" s="4" t="s">
-        <v>4</v>
+      <c r="I724" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="725" spans="1:9" x14ac:dyDescent="0.2">
@@ -21731,8 +21738,8 @@
       <c r="H725" s="4">
         <v>42</v>
       </c>
-      <c r="I725" s="4" t="s">
-        <v>5</v>
+      <c r="I725" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="726" spans="1:9" x14ac:dyDescent="0.2">
@@ -21760,8 +21767,8 @@
       <c r="H726" s="4">
         <v>45</v>
       </c>
-      <c r="I726" s="4" t="s">
-        <v>5</v>
+      <c r="I726" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="727" spans="1:9" x14ac:dyDescent="0.2">
@@ -21789,8 +21796,8 @@
       <c r="H727" s="4">
         <v>38</v>
       </c>
-      <c r="I727" s="4" t="s">
-        <v>5</v>
+      <c r="I727" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="728" spans="1:9" x14ac:dyDescent="0.2">
@@ -21818,8 +21825,8 @@
       <c r="H728" s="4">
         <v>25</v>
       </c>
-      <c r="I728" s="4" t="s">
-        <v>5</v>
+      <c r="I728" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="729" spans="1:9" x14ac:dyDescent="0.2">
@@ -21847,8 +21854,8 @@
       <c r="H729" s="4">
         <v>22</v>
       </c>
-      <c r="I729" s="4" t="s">
-        <v>5</v>
+      <c r="I729" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="730" spans="1:9" x14ac:dyDescent="0.2">
@@ -21876,8 +21883,8 @@
       <c r="H730" s="4">
         <v>22</v>
       </c>
-      <c r="I730" s="4" t="s">
-        <v>5</v>
+      <c r="I730" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.2">
@@ -21905,8 +21912,8 @@
       <c r="H731" s="4">
         <v>22</v>
       </c>
-      <c r="I731" s="4" t="s">
-        <v>5</v>
+      <c r="I731" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="732" spans="1:9" x14ac:dyDescent="0.2">
@@ -21934,8 +21941,8 @@
       <c r="H732" s="4">
         <v>34</v>
       </c>
-      <c r="I732" s="4" t="s">
-        <v>4</v>
+      <c r="I732" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="733" spans="1:9" x14ac:dyDescent="0.2">
@@ -21963,8 +21970,8 @@
       <c r="H733" s="4">
         <v>22</v>
       </c>
-      <c r="I733" s="4" t="s">
-        <v>4</v>
+      <c r="I733" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="734" spans="1:9" x14ac:dyDescent="0.2">
@@ -21992,8 +21999,8 @@
       <c r="H734" s="4">
         <v>24</v>
       </c>
-      <c r="I734" s="4" t="s">
-        <v>4</v>
+      <c r="I734" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.2">
@@ -22021,8 +22028,8 @@
       <c r="H735" s="4">
         <v>22</v>
       </c>
-      <c r="I735" s="4" t="s">
-        <v>5</v>
+      <c r="I735" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="736" spans="1:9" x14ac:dyDescent="0.2">
@@ -22050,8 +22057,8 @@
       <c r="H736" s="4">
         <v>53</v>
       </c>
-      <c r="I736" s="4" t="s">
-        <v>5</v>
+      <c r="I736" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="737" spans="1:9" x14ac:dyDescent="0.2">
@@ -22079,8 +22086,8 @@
       <c r="H737" s="4">
         <v>28</v>
       </c>
-      <c r="I737" s="4" t="s">
-        <v>5</v>
+      <c r="I737" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="738" spans="1:9" x14ac:dyDescent="0.2">
@@ -22108,8 +22115,8 @@
       <c r="H738" s="4">
         <v>21</v>
       </c>
-      <c r="I738" s="4" t="s">
-        <v>5</v>
+      <c r="I738" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="739" spans="1:9" x14ac:dyDescent="0.2">
@@ -22137,8 +22144,8 @@
       <c r="H739" s="4">
         <v>42</v>
       </c>
-      <c r="I739" s="4" t="s">
-        <v>5</v>
+      <c r="I739" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="740" spans="1:9" x14ac:dyDescent="0.2">
@@ -22166,8 +22173,8 @@
       <c r="H740" s="4">
         <v>21</v>
       </c>
-      <c r="I740" s="4" t="s">
-        <v>5</v>
+      <c r="I740" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="741" spans="1:9" x14ac:dyDescent="0.2">
@@ -22195,8 +22202,8 @@
       <c r="H741" s="4">
         <v>42</v>
       </c>
-      <c r="I741" s="4" t="s">
-        <v>4</v>
+      <c r="I741" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="742" spans="1:9" x14ac:dyDescent="0.2">
@@ -22224,8 +22231,8 @@
       <c r="H742" s="4">
         <v>48</v>
       </c>
-      <c r="I742" s="4" t="s">
-        <v>4</v>
+      <c r="I742" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="743" spans="1:9" x14ac:dyDescent="0.2">
@@ -22253,8 +22260,8 @@
       <c r="H743" s="4">
         <v>26</v>
       </c>
-      <c r="I743" s="4" t="s">
-        <v>5</v>
+      <c r="I743" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="744" spans="1:9" x14ac:dyDescent="0.2">
@@ -22282,8 +22289,8 @@
       <c r="H744" s="4">
         <v>22</v>
       </c>
-      <c r="I744" s="4" t="s">
-        <v>5</v>
+      <c r="I744" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="745" spans="1:9" x14ac:dyDescent="0.2">
@@ -22311,8 +22318,8 @@
       <c r="H745" s="4">
         <v>45</v>
       </c>
-      <c r="I745" s="4" t="s">
-        <v>4</v>
+      <c r="I745" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="746" spans="1:9" x14ac:dyDescent="0.2">
@@ -22340,8 +22347,8 @@
       <c r="H746" s="4">
         <v>39</v>
       </c>
-      <c r="I746" s="4" t="s">
-        <v>5</v>
+      <c r="I746" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="747" spans="1:9" x14ac:dyDescent="0.2">
@@ -22369,8 +22376,8 @@
       <c r="H747" s="4">
         <v>46</v>
       </c>
-      <c r="I747" s="4" t="s">
-        <v>5</v>
+      <c r="I747" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="748" spans="1:9" x14ac:dyDescent="0.2">
@@ -22398,8 +22405,8 @@
       <c r="H748" s="4">
         <v>27</v>
       </c>
-      <c r="I748" s="4" t="s">
-        <v>4</v>
+      <c r="I748" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.2">
@@ -22427,8 +22434,8 @@
       <c r="H749" s="4">
         <v>32</v>
       </c>
-      <c r="I749" s="4" t="s">
-        <v>5</v>
+      <c r="I749" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="750" spans="1:9" x14ac:dyDescent="0.2">
@@ -22456,8 +22463,8 @@
       <c r="H750" s="4">
         <v>36</v>
       </c>
-      <c r="I750" s="4" t="s">
-        <v>4</v>
+      <c r="I750" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="751" spans="1:9" x14ac:dyDescent="0.2">
@@ -22485,8 +22492,8 @@
       <c r="H751" s="4">
         <v>50</v>
       </c>
-      <c r="I751" s="4" t="s">
-        <v>4</v>
+      <c r="I751" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="752" spans="1:9" x14ac:dyDescent="0.2">
@@ -22514,8 +22521,8 @@
       <c r="H752" s="4">
         <v>22</v>
       </c>
-      <c r="I752" s="4" t="s">
-        <v>4</v>
+      <c r="I752" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="753" spans="1:9" x14ac:dyDescent="0.2">
@@ -22543,8 +22550,8 @@
       <c r="H753" s="4">
         <v>28</v>
       </c>
-      <c r="I753" s="4" t="s">
-        <v>5</v>
+      <c r="I753" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="754" spans="1:9" x14ac:dyDescent="0.2">
@@ -22572,8 +22579,8 @@
       <c r="H754" s="4">
         <v>25</v>
       </c>
-      <c r="I754" s="4" t="s">
-        <v>5</v>
+      <c r="I754" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="755" spans="1:9" x14ac:dyDescent="0.2">
@@ -22601,8 +22608,8 @@
       <c r="H755" s="4">
         <v>26</v>
       </c>
-      <c r="I755" s="4" t="s">
-        <v>4</v>
+      <c r="I755" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="756" spans="1:9" x14ac:dyDescent="0.2">
@@ -22630,8 +22637,8 @@
       <c r="H756" s="4">
         <v>45</v>
       </c>
-      <c r="I756" s="4" t="s">
-        <v>4</v>
+      <c r="I756" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="757" spans="1:9" x14ac:dyDescent="0.2">
@@ -22659,8 +22666,8 @@
       <c r="H757" s="4">
         <v>37</v>
       </c>
-      <c r="I757" s="4" t="s">
-        <v>4</v>
+      <c r="I757" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="758" spans="1:9" x14ac:dyDescent="0.2">
@@ -22688,8 +22695,8 @@
       <c r="H758" s="4">
         <v>39</v>
       </c>
-      <c r="I758" s="4" t="s">
-        <v>5</v>
+      <c r="I758" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="759" spans="1:9" x14ac:dyDescent="0.2">
@@ -22717,8 +22724,8 @@
       <c r="H759" s="4">
         <v>52</v>
       </c>
-      <c r="I759" s="4" t="s">
-        <v>4</v>
+      <c r="I759" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="760" spans="1:9" x14ac:dyDescent="0.2">
@@ -22746,8 +22753,8 @@
       <c r="H760" s="4">
         <v>26</v>
       </c>
-      <c r="I760" s="4" t="s">
-        <v>5</v>
+      <c r="I760" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="761" spans="1:9" x14ac:dyDescent="0.2">
@@ -22775,8 +22782,8 @@
       <c r="H761" s="4">
         <v>66</v>
       </c>
-      <c r="I761" s="4" t="s">
-        <v>4</v>
+      <c r="I761" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.2">
@@ -22804,8 +22811,8 @@
       <c r="H762" s="4">
         <v>22</v>
       </c>
-      <c r="I762" s="4" t="s">
-        <v>5</v>
+      <c r="I762" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="763" spans="1:9" x14ac:dyDescent="0.2">
@@ -22833,8 +22840,8 @@
       <c r="H763" s="4">
         <v>43</v>
       </c>
-      <c r="I763" s="4" t="s">
-        <v>4</v>
+      <c r="I763" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="764" spans="1:9" x14ac:dyDescent="0.2">
@@ -22862,8 +22869,8 @@
       <c r="H764" s="4">
         <v>33</v>
       </c>
-      <c r="I764" s="4" t="s">
-        <v>5</v>
+      <c r="I764" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="765" spans="1:9" x14ac:dyDescent="0.2">
@@ -22891,8 +22898,8 @@
       <c r="H765" s="4">
         <v>63</v>
       </c>
-      <c r="I765" s="4" t="s">
-        <v>5</v>
+      <c r="I765" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="766" spans="1:9" x14ac:dyDescent="0.2">
@@ -22920,8 +22927,8 @@
       <c r="H766" s="4">
         <v>27</v>
       </c>
-      <c r="I766" s="4" t="s">
-        <v>5</v>
+      <c r="I766" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="767" spans="1:9" x14ac:dyDescent="0.2">
@@ -22949,8 +22956,8 @@
       <c r="H767" s="4">
         <v>30</v>
       </c>
-      <c r="I767" s="4" t="s">
-        <v>5</v>
+      <c r="I767" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="768" spans="1:9" x14ac:dyDescent="0.2">
@@ -22978,8 +22985,8 @@
       <c r="H768" s="4">
         <v>47</v>
       </c>
-      <c r="I768" s="4" t="s">
-        <v>4</v>
+      <c r="I768" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="769" spans="1:9" x14ac:dyDescent="0.2">
@@ -23007,8 +23014,8 @@
       <c r="H769" s="4">
         <v>23</v>
       </c>
-      <c r="I769" s="4" t="s">
-        <v>5</v>
+      <c r="I769" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
